--- a/tables/N-Retention/Local_estpar_protection_True_vo_True_CUE_True.xlsx
+++ b/tables/N-Retention/Local_estpar_protection_True_vo_True_CUE_True.xlsx
@@ -573,61 +573,61 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2306347362834478</v>
+        <v>0.1674339432438329</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2138961915032937</v>
+        <v>0.2034813240243573</v>
       </c>
       <c r="M2" t="n">
-        <v>4.412454985850541</v>
+        <v>4.387465324381761</v>
       </c>
       <c r="N2" t="n">
-        <v>4.428226414556559</v>
+        <v>4.42924271173901</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002588549693495138</v>
+        <v>0.003878323156063724</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002646436378490882</v>
+        <v>0.002523775395734312</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001251277236175246</v>
+        <v>0.0009392975410629365</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001000606580709318</v>
+        <v>0.0009389005941258131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00064187173088492</v>
+        <v>0.0005945499834903214</v>
       </c>
       <c r="T2" t="n">
-        <v>0.008252992551660461</v>
+        <v>0.01477363840689557</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005800364353345244</v>
+        <v>0.007002809530993873</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004268448647778354</v>
+        <v>0.002627170365035139</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001967377728112833</v>
+        <v>0.001924779402453914</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001579082063716852</v>
+        <v>0.00148059076929652</v>
       </c>
     </row>
     <row r="3">
@@ -653,61 +653,61 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1232120795919104</v>
+        <v>0.07218375034073646</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1575124506369778</v>
+        <v>0.1189172389508485</v>
       </c>
       <c r="M3" t="n">
-        <v>4.33964224043698</v>
+        <v>4.326733286264945</v>
       </c>
       <c r="N3" t="n">
-        <v>4.338584098574181</v>
+        <v>4.325782310005951</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002887478937961455</v>
+        <v>0.004688229443874862</v>
       </c>
       <c r="P3" t="n">
-        <v>1.000000019520939e-05</v>
+        <v>0.001469833702231356</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008902657142898381</v>
+        <v>0.000722055068871492</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005546228899882736</v>
+        <v>0.0004980631873617425</v>
       </c>
       <c r="S3" t="n">
-        <v>0.000319470322924298</v>
+        <v>0.0002809160785240437</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02469028719626875</v>
+        <v>0.02061295823199555</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1359919250524548</v>
+        <v>0.004255507497814426</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002735316389167787</v>
+        <v>0.001880151162293462</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001194722928736037</v>
+        <v>0.001120533677439074</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00112980231652526</v>
+        <v>0.001070909726216522</v>
       </c>
     </row>
     <row r="4">
@@ -733,61 +733,61 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4182134418056933</v>
+        <v>0.3797396150587981</v>
       </c>
       <c r="L4" t="n">
-        <v>0.22021503238386</v>
+        <v>0.3051920490125882</v>
       </c>
       <c r="M4" t="n">
-        <v>4.293495891699291</v>
+        <v>4.273399903936915</v>
       </c>
       <c r="N4" t="n">
-        <v>4.558564120740754</v>
+        <v>4.555785488299228</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002791085441924599</v>
+        <v>0.003468676080453266</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002317113645315102</v>
+        <v>0.002247650174599632</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0005257730474802713</v>
+        <v>0.0004274428942278988</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001144606538616994</v>
+        <v>0.001155861434633622</v>
       </c>
       <c r="S4" t="n">
-        <v>0.000260486108178834</v>
+        <v>0.0003478350916651518</v>
       </c>
       <c r="T4" t="n">
-        <v>0.008282400778978969</v>
+        <v>0.01165910382463223</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006153460347187814</v>
+        <v>0.006469192779620225</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002620951719292843</v>
+        <v>0.001853870513496701</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002079353022839611</v>
+        <v>0.002194945326944958</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001591060880566332</v>
+        <v>0.001773881347535981</v>
       </c>
     </row>
     <row r="5">
@@ -813,61 +813,61 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.183837851295302</v>
+        <v>0.1252238931351918</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2239793390830541</v>
+        <v>0.2163900068826985</v>
       </c>
       <c r="M5" t="n">
-        <v>4.308694500962631</v>
+        <v>4.317207381413163</v>
       </c>
       <c r="N5" t="n">
-        <v>4.348658192614951</v>
+        <v>4.351649457993587</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002359367870804973</v>
+        <v>0.003436307431659161</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002161679266971567</v>
+        <v>0.0001477589502922038</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001407036883212218</v>
+        <v>0.001102504153596598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0008342968463632691</v>
+        <v>0.0007951829552716863</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001161371717619072</v>
+        <v>0.001101120119013748</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007528554759361012</v>
+        <v>0.01379243392681677</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004340089858723221</v>
+        <v>0.07407736309376421</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004898430758193313</v>
+        <v>0.003265801735715035</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001660147482963122</v>
+        <v>0.002639146300595692</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002486561686288268</v>
+        <v>0.003115935829051753</v>
       </c>
     </row>
     <row r="6">
@@ -893,61 +893,61 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1701916451553553</v>
+        <v>0.1117312252274767</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2187774174871386</v>
+        <v>0.1726623846121318</v>
       </c>
       <c r="M6" t="n">
-        <v>4.378395834553357</v>
+        <v>4.373623920156238</v>
       </c>
       <c r="N6" t="n">
-        <v>4.391602973411937</v>
+        <v>4.375685617212183</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001896240074269396</v>
+        <v>0.002565694413123626</v>
       </c>
       <c r="P6" t="n">
-        <v>1.000000022104603e-05</v>
+        <v>0.001185332910102682</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009043815546474928</v>
+        <v>0.0006903226181669062</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003988810971391995</v>
+        <v>0.0003577487503136998</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003576133213860711</v>
+        <v>0.0003031378275598338</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01838116993012427</v>
+        <v>0.009165956387574815</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09540606551078006</v>
+        <v>0.002606802279343814</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00290740041213948</v>
+        <v>0.001934019419426883</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009876511143016625</v>
+        <v>0.0009373981384404091</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001061971512319022</v>
+        <v>0.0009820274000444686</v>
       </c>
     </row>
     <row r="7">
@@ -973,61 +973,61 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2317281644358207</v>
+        <v>0.1705952756742617</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1563852739568607</v>
+        <v>0.1606694045131564</v>
       </c>
       <c r="M7" t="n">
-        <v>4.265203801522019</v>
+        <v>4.238648069175182</v>
       </c>
       <c r="N7" t="n">
-        <v>4.379220734218603</v>
+        <v>4.381109138993254</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003256482880167089</v>
+        <v>0.004922089198390939</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001943047047868162</v>
+        <v>0.001820520116811419</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0007748850038877819</v>
+        <v>0.0006496482727826902</v>
       </c>
       <c r="R7" t="n">
-        <v>0.000911927674147022</v>
+        <v>0.0008614302569098123</v>
       </c>
       <c r="S7" t="n">
-        <v>0.000475933535642282</v>
+        <v>0.0004588738618155611</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01128928227704032</v>
+        <v>0.02021955538594497</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004643369438231179</v>
+        <v>0.005455975755287308</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002392825182781188</v>
+        <v>0.001755332070097749</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001724151777264424</v>
+        <v>0.001701219979307646</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001818927848610792</v>
+        <v>0.001836246400579191</v>
       </c>
     </row>
     <row r="8">
@@ -1053,61 +1053,61 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1755031604752748</v>
+        <v>0.1151345143695899</v>
       </c>
       <c r="L8" t="n">
-        <v>0.151574137268413</v>
+        <v>0.1546274117622884</v>
       </c>
       <c r="M8" t="n">
-        <v>4.444307466489452</v>
+        <v>4.414448270647104</v>
       </c>
       <c r="N8" t="n">
-        <v>4.408895309124271</v>
+        <v>4.413647468821939</v>
       </c>
       <c r="O8" t="n">
-        <v>0.005098226988423996</v>
+        <v>0.008756132338137853</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002808895987151166</v>
+        <v>0.003243536250562953</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001421312155948379</v>
+        <v>0.001164153145338074</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001446027052901157</v>
+        <v>0.001393348450984974</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00068443363205486</v>
+        <v>0.0006530221463527875</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02113830163577573</v>
+        <v>0.04538333434018352</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009241853718145565</v>
+        <v>0.01563964243627508</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004878045546893801</v>
+        <v>0.003294957631901291</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003121716325697483</v>
+        <v>0.003096312217660485</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001465037396426831</v>
+        <v>0.001384966255195734</v>
       </c>
     </row>
     <row r="9">
@@ -1133,61 +1133,61 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2153661717190752</v>
+        <v>0.1549872242120613</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1640503183193846</v>
+        <v>0.1626230395927207</v>
       </c>
       <c r="M9" t="n">
-        <v>4.234521484447876</v>
+        <v>4.210724940548642</v>
       </c>
       <c r="N9" t="n">
-        <v>4.363802685577269</v>
+        <v>4.363589432828832</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004327180465380977</v>
+        <v>0.006836218070934164</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002606254507378884</v>
+        <v>0.002670124643297046</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001103282522602693</v>
+        <v>0.0008926444270159549</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0009111837918610084</v>
+        <v>0.0008714111484796729</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0008130540168318312</v>
+        <v>0.0007854094721336098</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01574046691398548</v>
+        <v>0.03010848444365338</v>
       </c>
       <c r="U9" t="n">
-        <v>0.006728158267494454</v>
+        <v>0.009581155264252213</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003576522661494442</v>
+        <v>0.0024220103459016</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001755131060445136</v>
+        <v>0.001758210366128003</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001643712313263784</v>
+        <v>0.00160561441653613</v>
       </c>
     </row>
     <row r="10">
@@ -1213,61 +1213,61 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2184121894741882</v>
+        <v>0.1598414097710008</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1173379450768566</v>
+        <v>0.1273421002386755</v>
       </c>
       <c r="M10" t="n">
-        <v>4.11415328726214</v>
+        <v>4.094150303545265</v>
       </c>
       <c r="N10" t="n">
-        <v>4.236237903177271</v>
+        <v>4.237509690763194</v>
       </c>
       <c r="O10" t="n">
-        <v>0.004504591022741951</v>
+        <v>0.007494022900155392</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003053525329618362</v>
+        <v>0.003763846959964912</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0007341583740259797</v>
+        <v>0.0006361054394393403</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001016860764098526</v>
+        <v>0.0009627590862156589</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0005845216109780061</v>
+        <v>0.0005734026973644901</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01819955396571905</v>
+        <v>0.03809011591772418</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01017842189950281</v>
+        <v>0.01808412586598054</v>
       </c>
       <c r="V10" t="n">
-        <v>0.002178550305664131</v>
+        <v>0.001682326180610731</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001923676869067151</v>
+        <v>0.001910978645216298</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001307549323358849</v>
+        <v>0.001317847649744817</v>
       </c>
     </row>
     <row r="11">
@@ -1293,61 +1293,61 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4182813421933623</v>
+        <v>0.3840542250418848</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4001920703017508</v>
+        <v>0.3989843947473053</v>
       </c>
       <c r="M11" t="n">
-        <v>4.115746786233981</v>
+        <v>4.07733279147739</v>
       </c>
       <c r="N11" t="n">
-        <v>4.273412806917788</v>
+        <v>4.276708556000141</v>
       </c>
       <c r="O11" t="n">
-        <v>0.002351699121029789</v>
+        <v>0.003388907123435614</v>
       </c>
       <c r="P11" t="n">
-        <v>0.002068617301418585</v>
+        <v>0.001934684572741472</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.005827857700907084</v>
+        <v>0.002413029001165444</v>
       </c>
       <c r="R11" t="n">
-        <v>0.002544879090955412</v>
+        <v>0.002313040851189047</v>
       </c>
       <c r="S11" t="n">
-        <v>0.002067609686882035</v>
+        <v>0.001937430665447541</v>
       </c>
       <c r="T11" t="n">
-        <v>0.006597546020835168</v>
+        <v>0.01218854347415034</v>
       </c>
       <c r="U11" t="n">
-        <v>0.004096303557453297</v>
+        <v>0.003430356227639492</v>
       </c>
       <c r="V11" t="n">
-        <v>0.02839238516429414</v>
+        <v>0.008645386304665064</v>
       </c>
       <c r="W11" t="n">
-        <v>0.004155385757267048</v>
+        <v>0.003830746169750466</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003921444466545797</v>
+        <v>0.003644344382090137</v>
       </c>
     </row>
     <row r="12">
@@ -1373,61 +1373,61 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1412678730771366</v>
+        <v>0.08879437573964823</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2022582468825163</v>
+        <v>0.1748901279006494</v>
       </c>
       <c r="M12" t="n">
-        <v>4.107460678751526</v>
+        <v>4.097766389364954</v>
       </c>
       <c r="N12" t="n">
-        <v>4.144253061003062</v>
+        <v>4.131511182870908</v>
       </c>
       <c r="O12" t="n">
-        <v>0.001519838581723463</v>
+        <v>0.00217950822466531</v>
       </c>
       <c r="P12" t="n">
-        <v>0.002125148867943344</v>
+        <v>0.0009261733455108313</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.00109113679540286</v>
+        <v>0.0008014733309772902</v>
       </c>
       <c r="R12" t="n">
-        <v>0.002080664020065252</v>
+        <v>0.002041865925204744</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0006112387767316082</v>
+        <v>0.0005540053348333123</v>
       </c>
       <c r="T12" t="n">
-        <v>0.006040326157169534</v>
+        <v>0.01108137790450137</v>
       </c>
       <c r="U12" t="n">
-        <v>0.005017146011057447</v>
+        <v>0.005937037455030681</v>
       </c>
       <c r="V12" t="n">
-        <v>0.003802536904551216</v>
+        <v>0.002430990554729448</v>
       </c>
       <c r="W12" t="n">
-        <v>0.008903566673898794</v>
+        <v>0.01203960376118001</v>
       </c>
       <c r="X12" t="n">
-        <v>0.001366410814470482</v>
+        <v>0.001353507231067362</v>
       </c>
     </row>
     <row r="13">
@@ -1453,61 +1453,61 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3156537929037181</v>
+        <v>0.2601628982742144</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2726494720373033</v>
+        <v>0.2408719643652152</v>
       </c>
       <c r="M13" t="n">
-        <v>4.29263277483161</v>
+        <v>4.286409256864677</v>
       </c>
       <c r="N13" t="n">
-        <v>4.507431687309878</v>
+        <v>4.511612081318258</v>
       </c>
       <c r="O13" t="n">
-        <v>0.002706567352300211</v>
+        <v>0.00310583110334969</v>
       </c>
       <c r="P13" t="n">
-        <v>0.002203323442978637</v>
+        <v>0.002134797277046351</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.002093022212380996</v>
+        <v>0.001539079152552439</v>
       </c>
       <c r="R13" t="n">
-        <v>0.009236523175085018</v>
+        <v>0.00892781720425872</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01537915757586464</v>
+        <v>0.01505153427753973</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01481950106362037</v>
+        <v>0.01795892434935965</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03354118209583158</v>
+        <v>0.03140862185125241</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01326796886557</v>
+        <v>0.01003472604583846</v>
       </c>
       <c r="W13" t="n">
-        <v>0.01762465859769344</v>
+        <v>0.01742817152203452</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03715075234220446</v>
+        <v>0.03645421139021558</v>
       </c>
     </row>
     <row r="14">
@@ -1533,61 +1533,61 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2068452432900554</v>
+        <v>0.1445754358802914</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3499649854338223</v>
+        <v>0.2525870098598953</v>
       </c>
       <c r="M14" t="n">
-        <v>4.429062464935388</v>
+        <v>4.413656766676655</v>
       </c>
       <c r="N14" t="n">
-        <v>4.374958766769107</v>
+        <v>4.355574211319782</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01153322291965136</v>
+        <v>0.01555253190134656</v>
       </c>
       <c r="P14" t="n">
-        <v>1e-05</v>
+        <v>0.00117421807697506</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02632214351108464</v>
+        <v>0.01250845534515844</v>
       </c>
       <c r="R14" t="n">
-        <v>0.00829316077690836</v>
+        <v>0.006445133155352094</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0132181083199028</v>
+        <v>0.009650334708438225</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1428598115159009</v>
+        <v>0.05000016288672809</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5289908543220102</v>
+        <v>0.1131485178148813</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1158800521670088</v>
+        <v>0.03741218668566799</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01857693244922666</v>
+        <v>0.0145708809685322</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03785956481795309</v>
+        <v>0.02899305015759867</v>
       </c>
     </row>
     <row r="15">
@@ -1613,61 +1613,61 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1895470751595914</v>
+        <v>0.1316028009711741</v>
       </c>
       <c r="L15" t="n">
-        <v>0.29369105404012</v>
+        <v>0.2400705769377274</v>
       </c>
       <c r="M15" t="n">
-        <v>4.12729937470144</v>
+        <v>4.10389600519784</v>
       </c>
       <c r="N15" t="n">
-        <v>4.251286225585371</v>
+        <v>4.22981464645173</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01153787057806632</v>
+        <v>0.01524317318391451</v>
       </c>
       <c r="P15" t="n">
-        <v>0.00491396510312218</v>
+        <v>0.004201389691584724</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.01714618352170721</v>
+        <v>0.01199188534607597</v>
       </c>
       <c r="R15" t="n">
-        <v>0.005813051837501348</v>
+        <v>0.004871167445716138</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02602301365812578</v>
+        <v>0.02342819584117343</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03008980968168116</v>
+        <v>0.04633043987740341</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01420621379998798</v>
+        <v>0.01580429886900008</v>
       </c>
       <c r="V15" t="n">
-        <v>0.06147698604334072</v>
+        <v>0.03618794928201523</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01289384432520191</v>
+        <v>0.01178828241598582</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0922494979583097</v>
+        <v>0.08084481313307681</v>
       </c>
     </row>
     <row r="16">
@@ -1693,61 +1693,61 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5109637156163565</v>
+        <v>0.5058025943758175</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5248228053291905</v>
+        <v>0.511110244244519</v>
       </c>
       <c r="M16" t="n">
-        <v>4.305324632016705</v>
+        <v>4.349769392665977</v>
       </c>
       <c r="N16" t="n">
-        <v>4.499578138446319</v>
+        <v>4.49472646883386</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02795977037058923</v>
+        <v>0.02810439883375163</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01973319386874771</v>
+        <v>0.01938628811915379</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2494908810873907</v>
+        <v>0.05188156448837034</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01289464404103659</v>
+        <v>0.01227263702583894</v>
       </c>
       <c r="S16" t="n">
-        <v>0.03895640810840645</v>
+        <v>0.01882851590407672</v>
       </c>
       <c r="T16" t="n">
-        <v>0.08300044579389146</v>
+        <v>0.1330096261850886</v>
       </c>
       <c r="U16" t="n">
-        <v>0.03064668158106581</v>
+        <v>0.07189983533492456</v>
       </c>
       <c r="V16" t="n">
-        <v>14.77209280393934</v>
+        <v>1.114022073397786</v>
       </c>
       <c r="W16" t="n">
-        <v>0.05918381767874265</v>
+        <v>0.01941348160139615</v>
       </c>
       <c r="X16" t="n">
-        <v>62.19966838387636</v>
+        <v>23.14791809572846</v>
       </c>
     </row>
     <row r="17">
@@ -1773,61 +1773,61 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2121923977296436</v>
+        <v>0.1560962956401372</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2665789940031534</v>
+        <v>0.2176141117888516</v>
       </c>
       <c r="M17" t="n">
-        <v>3.89038661935276</v>
+        <v>3.850449758009987</v>
       </c>
       <c r="N17" t="n">
-        <v>4.034613591520077</v>
+        <v>4.003355433840693</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01288711428302649</v>
+        <v>0.01666553333665856</v>
       </c>
       <c r="P17" t="n">
-        <v>0.003190064221479298</v>
+        <v>0.002197486440482451</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01346774475788557</v>
+        <v>0.01002107382384962</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004645011054072682</v>
+        <v>0.003776831460417556</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01072279547415777</v>
+        <v>0.01035570677527403</v>
       </c>
       <c r="T17" t="n">
-        <v>0.03301666972145288</v>
+        <v>0.04892807629792244</v>
       </c>
       <c r="U17" t="n">
-        <v>0.01850677895024875</v>
+        <v>0.01617964664858214</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0438496116080137</v>
+        <v>0.02853311470594959</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0107794261488779</v>
+        <v>0.009876345471894084</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02091788700540495</v>
+        <v>0.02039276390262555</v>
       </c>
     </row>
     <row r="18">
@@ -1853,61 +1853,61 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.24258952682581</v>
+        <v>0.181582972876025</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2660266826871621</v>
+        <v>0.2291146013485572</v>
       </c>
       <c r="M18" t="n">
-        <v>4.300562681691318</v>
+        <v>4.287479093745305</v>
       </c>
       <c r="N18" t="n">
-        <v>4.300495078191944</v>
+        <v>4.290261353909024</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0132376709096335</v>
+        <v>0.01753672101882884</v>
       </c>
       <c r="P18" t="n">
-        <v>0.00681129232931395</v>
+        <v>0.006870036782572463</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.01171949635204929</v>
+        <v>0.008715530420308126</v>
       </c>
       <c r="R18" t="n">
-        <v>0.00849322490141575</v>
+        <v>0.007720678040889745</v>
       </c>
       <c r="S18" t="n">
-        <v>0.008848764120452022</v>
+        <v>0.008261082358081404</v>
       </c>
       <c r="T18" t="n">
-        <v>0.03396721605044127</v>
+        <v>0.05164777757734745</v>
       </c>
       <c r="U18" t="n">
-        <v>0.01541847042973249</v>
+        <v>0.0180420084871737</v>
       </c>
       <c r="V18" t="n">
-        <v>0.03681490085125969</v>
+        <v>0.02397901788142032</v>
       </c>
       <c r="W18" t="n">
-        <v>0.01494770064066304</v>
+        <v>0.01425800340100273</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01553792814555296</v>
+        <v>0.01484889274857591</v>
       </c>
     </row>
     <row r="19">
@@ -1933,61 +1933,61 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1618647634163979</v>
+        <v>0.1080512787950732</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2267943694544231</v>
+        <v>0.1791781034397167</v>
       </c>
       <c r="M19" t="n">
-        <v>4.01013022703957</v>
+        <v>4.009989320724906</v>
       </c>
       <c r="N19" t="n">
-        <v>4.381077920595329</v>
+        <v>4.370018245738256</v>
       </c>
       <c r="O19" t="n">
-        <v>0.004872206345465319</v>
+        <v>0.006290359912523457</v>
       </c>
       <c r="P19" t="n">
-        <v>0.009584503966047387</v>
+        <v>0.009253317473517224</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.00567637946513994</v>
+        <v>0.004622994132354418</v>
       </c>
       <c r="R19" t="n">
-        <v>0.001511907495789723</v>
+        <v>0.001363803486557137</v>
       </c>
       <c r="S19" t="n">
-        <v>0.03178593550258741</v>
+        <v>0.02918612017959531</v>
       </c>
       <c r="T19" t="n">
-        <v>0.01913960821570984</v>
+        <v>0.02689310905183208</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02404432928852039</v>
+        <v>0.02579526438579246</v>
       </c>
       <c r="V19" t="n">
-        <v>0.01841223697550069</v>
+        <v>0.01428351500742926</v>
       </c>
       <c r="W19" t="n">
-        <v>0.006863433741323773</v>
+        <v>0.00662328925985413</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1605060758022008</v>
+        <v>0.1388125283573169</v>
       </c>
     </row>
     <row r="20">
@@ -2013,61 +2013,61 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.270337140109575</v>
+        <v>0.2057008732256997</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3065526125294156</v>
+        <v>0.252707072651963</v>
       </c>
       <c r="M20" t="n">
-        <v>4.622332151259288</v>
+        <v>4.630704694731168</v>
       </c>
       <c r="N20" t="n">
-        <v>4.58922304767674</v>
+        <v>4.594475229012931</v>
       </c>
       <c r="O20" t="n">
-        <v>0.00785931586429609</v>
+        <v>0.009872294106548635</v>
       </c>
       <c r="P20" t="n">
-        <v>0.001025000800824494</v>
+        <v>1.000000000000019e-05</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.009860404575518641</v>
+        <v>0.007137382040759152</v>
       </c>
       <c r="R20" t="n">
-        <v>0.005480568839047294</v>
+        <v>0.005058806643561632</v>
       </c>
       <c r="S20" t="n">
-        <v>0.01578174284774004</v>
+        <v>0.01312097949495857</v>
       </c>
       <c r="T20" t="n">
-        <v>0.02039597948269816</v>
+        <v>0.0282826994433424</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01580429778794902</v>
+        <v>0.01683493049796974</v>
       </c>
       <c r="V20" t="n">
-        <v>0.03100472001297187</v>
+        <v>0.0203756399269727</v>
       </c>
       <c r="W20" t="n">
-        <v>0.01141743107428418</v>
+        <v>0.01095269707200741</v>
       </c>
       <c r="X20" t="n">
-        <v>0.03092722591672567</v>
+        <v>0.02782289100854413</v>
       </c>
     </row>
     <row r="21">
@@ -2093,61 +2093,61 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1205682193591666</v>
+        <v>0.07288078000139452</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1423733601157885</v>
+        <v>0.136876123227639</v>
       </c>
       <c r="M21" t="n">
-        <v>4.116445283604787</v>
+        <v>4.177714502255803</v>
       </c>
       <c r="N21" t="n">
-        <v>4.12095334053991</v>
+        <v>4.130153181638189</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01478801104066373</v>
+        <v>0.01780058433932053</v>
       </c>
       <c r="P21" t="n">
-        <v>0.04991584459655532</v>
+        <v>0.06021739648152067</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.006895745083284601</v>
+        <v>0.00829291290901191</v>
       </c>
       <c r="R21" t="n">
-        <v>1.000000000000209e-05</v>
+        <v>1.000000000000064e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>1.00000000000495e-05</v>
+        <v>1.000000021545476e-05</v>
       </c>
       <c r="T21" t="n">
-        <v>0.05290185517907468</v>
+        <v>0.07839590074529819</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1596640232419171</v>
+        <v>0.2445336871846416</v>
       </c>
       <c r="V21" t="n">
-        <v>0.02511739227185156</v>
+        <v>0.0319129703818624</v>
       </c>
       <c r="W21" t="n">
-        <v>0.0112216396004246</v>
+        <v>0.01285682772051475</v>
       </c>
       <c r="X21" t="n">
-        <v>0.03925832733083881</v>
+        <v>0.05801580626211517</v>
       </c>
     </row>
     <row r="22">
@@ -2173,61 +2173,61 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3067591657776431</v>
+        <v>0.2533994605117408</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3269822380030594</v>
+        <v>0.2796877818453221</v>
       </c>
       <c r="M22" t="n">
-        <v>4.138954932523397</v>
+        <v>4.12741070069084</v>
       </c>
       <c r="N22" t="n">
-        <v>4.310398876090731</v>
+        <v>4.298014114122767</v>
       </c>
       <c r="O22" t="n">
-        <v>0.005703698820713233</v>
+        <v>0.006817344245350855</v>
       </c>
       <c r="P22" t="n">
-        <v>4.788112908596861e-05</v>
+        <v>1.000000000000001e-05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.006835433377090532</v>
+        <v>0.004992983105345955</v>
       </c>
       <c r="R22" t="n">
-        <v>0.003432013172883334</v>
+        <v>0.003196624357946525</v>
       </c>
       <c r="S22" t="n">
-        <v>0.01268007102248277</v>
+        <v>0.01205767744382579</v>
       </c>
       <c r="T22" t="n">
-        <v>0.01611841306833972</v>
+        <v>0.02012359538097784</v>
       </c>
       <c r="U22" t="n">
-        <v>0.01336098278259638</v>
+        <v>0.01278669684914623</v>
       </c>
       <c r="V22" t="n">
-        <v>0.02649187867850485</v>
+        <v>0.01845404951752473</v>
       </c>
       <c r="W22" t="n">
-        <v>0.009129540545848667</v>
+        <v>0.008751757135339943</v>
       </c>
       <c r="X22" t="n">
-        <v>0.02736140892142187</v>
+        <v>0.02617809791309104</v>
       </c>
     </row>
     <row r="23">
@@ -2253,61 +2253,61 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2857369714597892</v>
+        <v>0.236563796036645</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2866928234677282</v>
+        <v>0.2488981055580513</v>
       </c>
       <c r="M23" t="n">
-        <v>3.863757349446638</v>
+        <v>3.857771998428968</v>
       </c>
       <c r="N23" t="n">
-        <v>4.120439229326817</v>
+        <v>4.099638800599722</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01077258601844725</v>
+        <v>0.01392313811048928</v>
       </c>
       <c r="P23" t="n">
-        <v>0.004341422011590514</v>
+        <v>0.00388721889556345</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.009164585715531295</v>
+        <v>0.006402240154923932</v>
       </c>
       <c r="R23" t="n">
-        <v>0.006675871266678195</v>
+        <v>0.005488679485051984</v>
       </c>
       <c r="S23" t="n">
-        <v>0.02494179322274812</v>
+        <v>0.02327877862498233</v>
       </c>
       <c r="T23" t="n">
-        <v>0.02767837191543094</v>
+        <v>0.04044989455458865</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01869705401335302</v>
+        <v>0.01784227202313129</v>
       </c>
       <c r="V23" t="n">
-        <v>0.02994334654795782</v>
+        <v>0.01923262210364536</v>
       </c>
       <c r="W23" t="n">
-        <v>0.01232616657327023</v>
+        <v>0.01148463973638204</v>
       </c>
       <c r="X23" t="n">
-        <v>0.07753349631854506</v>
+        <v>0.07076795294784202</v>
       </c>
     </row>
     <row r="24">
@@ -2333,61 +2333,61 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3899491530645845</v>
+        <v>0.3438194492405634</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4738363484336767</v>
+        <v>0.437378249201195</v>
       </c>
       <c r="M24" t="n">
-        <v>4.330915049849626</v>
+        <v>4.306058852366302</v>
       </c>
       <c r="N24" t="n">
-        <v>4.386143874223134</v>
+        <v>4.362088745449129</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01270831934923817</v>
+        <v>0.01423551908088942</v>
       </c>
       <c r="P24" t="n">
-        <v>0.009365876712975773</v>
+        <v>0.009555158334524815</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.09201728505651084</v>
+        <v>0.03731791514541583</v>
       </c>
       <c r="R24" t="n">
-        <v>0.01374423130417479</v>
+        <v>0.0123537954402443</v>
       </c>
       <c r="S24" t="n">
-        <v>1.000000000093162e-05</v>
+        <v>1.000000000000118e-05</v>
       </c>
       <c r="T24" t="n">
-        <v>0.03005267218255816</v>
+        <v>0.04996179553438058</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0174588122687918</v>
+        <v>0.02531212413221801</v>
       </c>
       <c r="V24" t="n">
-        <v>0.957382973086685</v>
+        <v>0.3016128715086063</v>
       </c>
       <c r="W24" t="n">
-        <v>0.022327840589088</v>
+        <v>0.02272787044231356</v>
       </c>
       <c r="X24" t="n">
-        <v>1.070619086120369</v>
+        <v>1.672168558357028</v>
       </c>
     </row>
     <row r="25">
@@ -2413,61 +2413,61 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2158934749426978</v>
+        <v>0.1556531723472595</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2288212176259103</v>
+        <v>0.1799981948277626</v>
       </c>
       <c r="M25" t="n">
-        <v>4.311008836928643</v>
+        <v>4.318162033299422</v>
       </c>
       <c r="N25" t="n">
-        <v>4.340698822330908</v>
+        <v>4.341389638091139</v>
       </c>
       <c r="O25" t="n">
-        <v>0.002227050793343374</v>
+        <v>0.002989582916939963</v>
       </c>
       <c r="P25" t="n">
-        <v>1.000000000000249e-05</v>
+        <v>1.000000000013433e-05</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0009272596949026803</v>
+        <v>0.0008429935862196409</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0003337747272566673</v>
+        <v>0.0003187777235327907</v>
       </c>
       <c r="S25" t="n">
-        <v>9.830293358068274e-05</v>
+        <v>7.337609308982667e-05</v>
       </c>
       <c r="T25" t="n">
-        <v>0.005445970633114964</v>
+        <v>0.008007604718600316</v>
       </c>
       <c r="U25" t="n">
-        <v>0.002891211546329953</v>
+        <v>0.003273380797079072</v>
       </c>
       <c r="V25" t="n">
-        <v>0.003144059723205296</v>
+        <v>0.002629735058687421</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001343883601891845</v>
+        <v>0.001316430220211471</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001314232368928139</v>
+        <v>0.001298921092651921</v>
       </c>
     </row>
     <row r="26">
@@ -2493,61 +2493,61 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.319605401855295</v>
+        <v>0.2654673820478013</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3067566003139182</v>
+        <v>0.2647920494983484</v>
       </c>
       <c r="M26" t="n">
-        <v>4.221808346553291</v>
+        <v>4.203760876198466</v>
       </c>
       <c r="N26" t="n">
-        <v>4.299252264058017</v>
+        <v>4.287929336576728</v>
       </c>
       <c r="O26" t="n">
-        <v>0.002895729894423425</v>
+        <v>0.003553513156912719</v>
       </c>
       <c r="P26" t="n">
-        <v>0.001540869741159283</v>
+        <v>0.001334508429188928</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.001530688559659498</v>
+        <v>0.001077203479874421</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0005610067201126984</v>
+        <v>0.0004960517045919929</v>
       </c>
       <c r="S26" t="n">
-        <v>0.000320505036665777</v>
+        <v>0.0002768043466932458</v>
       </c>
       <c r="T26" t="n">
-        <v>0.005815480477789379</v>
+        <v>0.007738924825548683</v>
       </c>
       <c r="U26" t="n">
-        <v>0.002436834387079412</v>
+        <v>0.002345317387659328</v>
       </c>
       <c r="V26" t="n">
-        <v>0.005128512473180752</v>
+        <v>0.003423105226798544</v>
       </c>
       <c r="W26" t="n">
-        <v>0.001509443271880516</v>
+        <v>0.001457587125908658</v>
       </c>
       <c r="X26" t="n">
-        <v>0.001258773084795716</v>
+        <v>0.001236541296998774</v>
       </c>
     </row>
     <row r="27">
@@ -2573,61 +2573,61 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2452896402637705</v>
+        <v>0.1860906494832026</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3103151281310915</v>
+        <v>0.2609263764648936</v>
       </c>
       <c r="M27" t="n">
-        <v>4.171003209011483</v>
+        <v>4.150022463863345</v>
       </c>
       <c r="N27" t="n">
-        <v>4.14908671879705</v>
+        <v>4.128377186623956</v>
       </c>
       <c r="O27" t="n">
-        <v>0.001437276480514978</v>
+        <v>0.001717769227681431</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0005765645320171647</v>
+        <v>0.0003089896690472835</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.002832226853502619</v>
+        <v>0.002123112731797632</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0006441285626390565</v>
+        <v>0.0005393147709790656</v>
       </c>
       <c r="S27" t="n">
-        <v>0.000723606562769694</v>
+        <v>0.0006857694344910315</v>
       </c>
       <c r="T27" t="n">
-        <v>0.003444973016160398</v>
+        <v>0.004504618205352874</v>
       </c>
       <c r="U27" t="n">
-        <v>0.002439560836847509</v>
+        <v>0.002448038014065887</v>
       </c>
       <c r="V27" t="n">
-        <v>0.009038235150673847</v>
+        <v>0.006131222436242601</v>
       </c>
       <c r="W27" t="n">
-        <v>0.00172238019203396</v>
+        <v>0.001627411464295071</v>
       </c>
       <c r="X27" t="n">
-        <v>0.001795122101848619</v>
+        <v>0.001768716077328466</v>
       </c>
     </row>
     <row r="28">
@@ -2653,61 +2653,61 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3983433844077345</v>
+        <v>0.3628997599405132</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4053307994278558</v>
+        <v>0.3889961231312799</v>
       </c>
       <c r="M28" t="n">
-        <v>4.109024519998804</v>
+        <v>4.105048742406989</v>
       </c>
       <c r="N28" t="n">
-        <v>4.291467552638386</v>
+        <v>4.286841258219166</v>
       </c>
       <c r="O28" t="n">
-        <v>0.002072957487608825</v>
+        <v>0.002327585182824392</v>
       </c>
       <c r="P28" t="n">
         <v>1e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.005863194428120325</v>
+        <v>0.003750470988081168</v>
       </c>
       <c r="R28" t="n">
-        <v>0.004994584985539023</v>
+        <v>0.004891282785943639</v>
       </c>
       <c r="S28" t="n">
-        <v>0.01033426407026321</v>
+        <v>0.01004340971661274</v>
       </c>
       <c r="T28" t="n">
-        <v>0.004751802028760859</v>
+        <v>0.005731329136174606</v>
       </c>
       <c r="U28" t="n">
-        <v>0.01082367452556427</v>
+        <v>0.01051632903110562</v>
       </c>
       <c r="V28" t="n">
-        <v>0.01889571055017876</v>
+        <v>0.01066528431710511</v>
       </c>
       <c r="W28" t="n">
-        <v>0.009508325109006293</v>
+        <v>0.01008378282648866</v>
       </c>
       <c r="X28" t="n">
-        <v>0.02337551833707202</v>
+        <v>0.02286036847442736</v>
       </c>
     </row>
     <row r="29">
@@ -2733,61 +2733,61 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5340055862294603</v>
+        <v>0.5406426407248554</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3537511708827761</v>
+        <v>0.5160117356780172</v>
       </c>
       <c r="M29" t="n">
-        <v>4.257333241600258</v>
+        <v>4.311389929681745</v>
       </c>
       <c r="N29" t="n">
-        <v>4.213034118342315</v>
+        <v>4.268701719023421</v>
       </c>
       <c r="O29" t="n">
-        <v>0.004706119344066876</v>
+        <v>0.004208460938638278</v>
       </c>
       <c r="P29" t="n">
-        <v>0.01781406183477655</v>
+        <v>0.01898441589271225</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.001112501966933918</v>
+        <v>0.001118501547823159</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01718721293510463</v>
+        <v>0.02092074429580722</v>
       </c>
       <c r="S29" t="n">
-        <v>0.009435734175553634</v>
+        <v>0.01041158193496168</v>
       </c>
       <c r="T29" t="n">
-        <v>0.008991775749481973</v>
+        <v>0.007153637877931236</v>
       </c>
       <c r="U29" t="n">
-        <v>0.06048863068591687</v>
+        <v>0.0741560046989375</v>
       </c>
       <c r="V29" t="n">
-        <v>0.009328677827489671</v>
+        <v>0.004328849056691108</v>
       </c>
       <c r="W29" t="n">
-        <v>0.03271838197794723</v>
+        <v>0.04647781886524555</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01595010890889274</v>
+        <v>0.01790096064573862</v>
       </c>
     </row>
     <row r="30">
@@ -2813,61 +2813,61 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5325113215269579</v>
+        <v>0.5203645174949575</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4061304465257691</v>
+        <v>0.4550983073930383</v>
       </c>
       <c r="M30" t="n">
-        <v>4.515704212940665</v>
+        <v>4.521684421917743</v>
       </c>
       <c r="N30" t="n">
-        <v>4.313476688440938</v>
+        <v>4.320995465016888</v>
       </c>
       <c r="O30" t="n">
-        <v>0.002631675296002269</v>
+        <v>0.002806319221581722</v>
       </c>
       <c r="P30" t="n">
-        <v>0.005031330023717456</v>
+        <v>0.004853145157147365</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.001786660745794534</v>
+        <v>0.0009783322415043436</v>
       </c>
       <c r="R30" t="n">
-        <v>0.009646846455257692</v>
+        <v>0.01013081764483238</v>
       </c>
       <c r="S30" t="n">
-        <v>0.004262691165186872</v>
+        <v>0.004574722309944441</v>
       </c>
       <c r="T30" t="n">
-        <v>0.005072249298934754</v>
+        <v>0.00558340064939418</v>
       </c>
       <c r="U30" t="n">
-        <v>0.009009373155821678</v>
+        <v>0.00833452059583161</v>
       </c>
       <c r="V30" t="n">
-        <v>0.01394959707593543</v>
+        <v>0.006815552034330685</v>
       </c>
       <c r="W30" t="n">
-        <v>0.01632521069276819</v>
+        <v>0.01796309983219939</v>
       </c>
       <c r="X30" t="n">
-        <v>0.005620439841438554</v>
+        <v>0.006085776878954841</v>
       </c>
     </row>
     <row r="31">
@@ -2893,61 +2893,61 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4901448304506785</v>
+        <v>0.4758642080817636</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4307997022511386</v>
+        <v>0.4406806010885068</v>
       </c>
       <c r="M31" t="n">
-        <v>4.249026147841872</v>
+        <v>4.25445111063005</v>
       </c>
       <c r="N31" t="n">
-        <v>4.408930889587362</v>
+        <v>4.40692901143991</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002771812191914096</v>
+        <v>0.002896833466915962</v>
       </c>
       <c r="P31" t="n">
-        <v>0.007349276814842575</v>
+        <v>0.006979953479778965</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.001566470648079969</v>
+        <v>0.0008208872974695813</v>
       </c>
       <c r="R31" t="n">
-        <v>0.001811076871221427</v>
+        <v>0.001813080468693583</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0005777036260591665</v>
+        <v>0.0005815794138276866</v>
       </c>
       <c r="T31" t="n">
-        <v>0.005009747952420827</v>
+        <v>0.005378205838510211</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01717453529252223</v>
+        <v>0.01520734795926888</v>
       </c>
       <c r="V31" t="n">
-        <v>0.01294604338786009</v>
+        <v>0.006290688468045455</v>
       </c>
       <c r="W31" t="n">
-        <v>0.002981214292240811</v>
+        <v>0.003101129852167588</v>
       </c>
       <c r="X31" t="n">
-        <v>0.002777060325854031</v>
+        <v>0.002830260208189001</v>
       </c>
     </row>
     <row r="32">
@@ -2973,61 +2973,61 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5003028185540506</v>
+        <v>0.4784031200138491</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4274257323699956</v>
+        <v>0.4392796549618741</v>
       </c>
       <c r="M32" t="n">
-        <v>4.530139452862152</v>
+        <v>4.543747350314697</v>
       </c>
       <c r="N32" t="n">
-        <v>4.426366733301174</v>
+        <v>4.423271470040162</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0008333218414156414</v>
+        <v>0.0009142669654756379</v>
       </c>
       <c r="P32" t="n">
-        <v>0.005242317589998033</v>
+        <v>0.005177174879196569</v>
       </c>
       <c r="Q32" t="n">
         <v>1e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.00440900614646704</v>
+        <v>0.004553087041111755</v>
       </c>
       <c r="S32" t="n">
-        <v>0.00139890869216171</v>
+        <v>0.001421900330206515</v>
       </c>
       <c r="T32" t="n">
-        <v>0.002812879990652049</v>
+        <v>0.003079277993690341</v>
       </c>
       <c r="U32" t="n">
-        <v>0.01135121579130941</v>
+        <v>0.01090292616308419</v>
       </c>
       <c r="V32" t="n">
-        <v>0.0112527633064123</v>
+        <v>0.00690587100610414</v>
       </c>
       <c r="W32" t="n">
-        <v>0.008038982106448744</v>
+        <v>0.008675892082943424</v>
       </c>
       <c r="X32" t="n">
-        <v>0.003574017750836421</v>
+        <v>0.003638539412270129</v>
       </c>
     </row>
     <row r="33">
@@ -3051,61 +3051,61 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2845720576653915</v>
+        <v>0.2253351707878397</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3094853665471586</v>
+        <v>0.2837466557410158</v>
       </c>
       <c r="M33" t="n">
-        <v>4.300519149462805</v>
+        <v>4.284692602034447</v>
       </c>
       <c r="N33" t="n">
-        <v>4.268789356988536</v>
+        <v>4.261031171421288</v>
       </c>
       <c r="O33" t="n">
-        <v>0.006459786430733619</v>
+        <v>0.008115100619960626</v>
       </c>
       <c r="P33" t="n">
-        <v>0.00399209826014126</v>
+        <v>0.002125819784889603</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.008740491515353622</v>
+        <v>0.006162918274277718</v>
       </c>
       <c r="R33" t="n">
-        <v>0.00740634246084285</v>
+        <v>0.006758154152190116</v>
       </c>
       <c r="S33" t="n">
-        <v>0.004069966116854634</v>
+        <v>0.003724652038501375</v>
       </c>
       <c r="T33" t="n">
-        <v>0.01754609504531611</v>
+        <v>0.02613761107579867</v>
       </c>
       <c r="U33" t="n">
-        <v>0.02441502329541632</v>
+        <v>0.01992965701022312</v>
       </c>
       <c r="V33" t="n">
-        <v>0.03359882083314529</v>
+        <v>0.01973016690136992</v>
       </c>
       <c r="W33" t="n">
-        <v>0.01425906458768727</v>
+        <v>0.01427286197100559</v>
       </c>
       <c r="X33" t="n">
-        <v>0.007911558518548282</v>
+        <v>0.007611593408086906</v>
       </c>
     </row>
     <row r="34">
@@ -3131,61 +3131,61 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5337173211659239</v>
+        <v>0.5349204065807047</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4594789794307157</v>
+        <v>0.5197406872727356</v>
       </c>
       <c r="M34" t="n">
-        <v>4.254011730907492</v>
+        <v>4.266981556961285</v>
       </c>
       <c r="N34" t="n">
-        <v>4.290063054664384</v>
+        <v>4.309138203257641</v>
       </c>
       <c r="O34" t="n">
-        <v>0.005293537958390806</v>
+        <v>0.00628782296019729</v>
       </c>
       <c r="P34" t="n">
-        <v>0.01449325049678961</v>
+        <v>0.01467439651491651</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.02173365729682402</v>
+        <v>0.004578528656272019</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01405915792835894</v>
+        <v>0.0169074716336018</v>
       </c>
       <c r="S34" t="n">
-        <v>0.008223738851225243</v>
+        <v>0.01007384153344677</v>
       </c>
       <c r="T34" t="n">
-        <v>0.007883139557382282</v>
+        <v>0.009936572049361467</v>
       </c>
       <c r="U34" t="n">
-        <v>0.05427348058791771</v>
+        <v>0.05720527863386792</v>
       </c>
       <c r="V34" t="n">
-        <v>0.08259749265859682</v>
+        <v>0.007451586020058591</v>
       </c>
       <c r="W34" t="n">
-        <v>0.01769669622720369</v>
+        <v>0.02172882129978074</v>
       </c>
       <c r="X34" t="n">
-        <v>0.00716031978545314</v>
+        <v>0.008510070342187705</v>
       </c>
     </row>
     <row r="35">
@@ -3211,61 +3211,61 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3017567405934108</v>
+        <v>0.2503626538263644</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2446039175795452</v>
+        <v>0.2453795286280497</v>
       </c>
       <c r="M35" t="n">
-        <v>4.047146068348874</v>
+        <v>4.042303821541178</v>
       </c>
       <c r="N35" t="n">
-        <v>4.156055410298507</v>
+        <v>4.151387123043699</v>
       </c>
       <c r="O35" t="n">
-        <v>0.002591332400424746</v>
+        <v>0.003414373605622675</v>
       </c>
       <c r="P35" t="n">
-        <v>0.05839057765869057</v>
+        <v>0.07099712768706633</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.001164952168749607</v>
+        <v>0.0008715678302221226</v>
       </c>
       <c r="R35" t="n">
-        <v>0.004759437049525006</v>
+        <v>0.004589076205805081</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0009506602365975521</v>
+        <v>0.0009287545709174635</v>
       </c>
       <c r="T35" t="n">
-        <v>0.01243090473175927</v>
+        <v>0.01611089855860847</v>
       </c>
       <c r="U35" t="n">
-        <v>26.22187932220613</v>
+        <v>37.08922309558062</v>
       </c>
       <c r="V35" t="n">
-        <v>0.006920718809434856</v>
+        <v>0.00412076659259366</v>
       </c>
       <c r="W35" t="n">
-        <v>0.0224981326684356</v>
+        <v>0.01603199649632354</v>
       </c>
       <c r="X35" t="n">
-        <v>0.002626807572345213</v>
+        <v>0.002516073717486858</v>
       </c>
     </row>
     <row r="36">
@@ -3291,61 +3291,61 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4303510992459229</v>
+        <v>0.3952543891983995</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3939800805864314</v>
+        <v>0.3747781148056714</v>
       </c>
       <c r="M36" t="n">
-        <v>4.305403694774172</v>
+        <v>4.294431636644179</v>
       </c>
       <c r="N36" t="n">
-        <v>4.32080620179621</v>
+        <v>4.314044964815882</v>
       </c>
       <c r="O36" t="n">
-        <v>0.001354609422965776</v>
+        <v>0.001492384113974396</v>
       </c>
       <c r="P36" t="n">
-        <v>0.002766124108187839</v>
+        <v>0.002641666187450695</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.001606529954626481</v>
+        <v>0.001017956687124919</v>
       </c>
       <c r="R36" t="n">
-        <v>0.00193283348767519</v>
+        <v>0.001818642362291593</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001309712328047509</v>
+        <v>0.001238512457880979</v>
       </c>
       <c r="T36" t="n">
-        <v>0.00357449806879154</v>
+        <v>0.00410114037856216</v>
       </c>
       <c r="U36" t="n">
-        <v>0.006171265407889702</v>
+        <v>0.005823012244503736</v>
       </c>
       <c r="V36" t="n">
-        <v>0.01083814594914742</v>
+        <v>0.006833825909894108</v>
       </c>
       <c r="W36" t="n">
-        <v>0.00360372821623126</v>
+        <v>0.003536142813104424</v>
       </c>
       <c r="X36" t="n">
-        <v>0.004516753479447161</v>
+        <v>0.004460046111833033</v>
       </c>
     </row>
     <row r="37">
@@ -3371,61 +3371,61 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1033156315000568</v>
+        <v>0.05739037544262496</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1059828642371518</v>
+        <v>0.07231248674386465</v>
       </c>
       <c r="M37" t="n">
-        <v>4.2322895226395</v>
+        <v>4.220030963149969</v>
       </c>
       <c r="N37" t="n">
-        <v>4.263470541648745</v>
+        <v>4.254880235658854</v>
       </c>
       <c r="O37" t="n">
-        <v>0.007601944601201592</v>
+        <v>0.01409299383830764</v>
       </c>
       <c r="P37" t="n">
-        <v>0.003361003954592212</v>
+        <v>0.003954565711144898</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.001413775568260181</v>
+        <v>0.001232243063209071</v>
       </c>
       <c r="R37" t="n">
-        <v>0.000843397419013481</v>
+        <v>0.0007393673710214549</v>
       </c>
       <c r="S37" t="n">
-        <v>0.002269007126178266</v>
+        <v>0.00195348610883983</v>
       </c>
       <c r="T37" t="n">
-        <v>0.02835794664986396</v>
+        <v>0.06179369845426744</v>
       </c>
       <c r="U37" t="n">
-        <v>0.009377544212304727</v>
+        <v>0.01511853165498354</v>
       </c>
       <c r="V37" t="n">
-        <v>0.004401015687790313</v>
+        <v>0.003600815012614599</v>
       </c>
       <c r="W37" t="n">
-        <v>0.002560594535593874</v>
+        <v>0.002463416353803291</v>
       </c>
       <c r="X37" t="n">
-        <v>0.005732714442660184</v>
+        <v>0.005022231249432033</v>
       </c>
     </row>
     <row r="38">
@@ -3451,61 +3451,61 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1414949912042679</v>
+        <v>0.08860067203198282</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1087290221050649</v>
+        <v>0.07286588812336381</v>
       </c>
       <c r="M38" t="n">
-        <v>4.109497407226164</v>
+        <v>4.08380765192147</v>
       </c>
       <c r="N38" t="n">
-        <v>4.195576882556786</v>
+        <v>4.186742415431928</v>
       </c>
       <c r="O38" t="n">
-        <v>0.009466158791810689</v>
+        <v>0.01816598417491</v>
       </c>
       <c r="P38" t="n">
-        <v>0.002600888321473296</v>
+        <v>0.004227706630053943</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0008554167754102429</v>
+        <v>0.0007082095574105887</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0004639389345015955</v>
+        <v>0.0003633383539267042</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0003912853955704609</v>
+        <v>1.164662717910109e-05</v>
       </c>
       <c r="T38" t="n">
-        <v>0.03180668575211528</v>
+        <v>0.06979823262080743</v>
       </c>
       <c r="U38" t="n">
-        <v>0.009225924844419304</v>
+        <v>0.01794262277099509</v>
       </c>
       <c r="V38" t="n">
-        <v>0.003383070468159375</v>
+        <v>0.002774645470050516</v>
       </c>
       <c r="W38" t="n">
-        <v>0.002123099521003483</v>
+        <v>0.00204844995178657</v>
       </c>
       <c r="X38" t="n">
-        <v>0.003150037007840459</v>
+        <v>0.002560507964710769</v>
       </c>
     </row>
     <row r="39">
@@ -3531,61 +3531,61 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1514588065490762</v>
+        <v>0.09603082938732513</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1342305756371794</v>
+        <v>0.09754471230093976</v>
       </c>
       <c r="M39" t="n">
-        <v>4.258033543989585</v>
+        <v>4.238213191185915</v>
       </c>
       <c r="N39" t="n">
-        <v>4.266426390932311</v>
+        <v>4.25765369969348</v>
       </c>
       <c r="O39" t="n">
-        <v>0.006470581946873035</v>
+        <v>0.01071137263928643</v>
       </c>
       <c r="P39" t="n">
-        <v>0.002042234687859863</v>
+        <v>0.001961444739868802</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.001427725333833631</v>
+        <v>0.001207864357196952</v>
       </c>
       <c r="R39" t="n">
-        <v>0.002326252982001576</v>
+        <v>0.002111422013714206</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001422625470839602</v>
+        <v>0.001326087434818644</v>
       </c>
       <c r="T39" t="n">
-        <v>0.01696030028570612</v>
+        <v>0.03147823833097897</v>
       </c>
       <c r="U39" t="n">
-        <v>0.009743853811556683</v>
+        <v>0.01336011302082606</v>
       </c>
       <c r="V39" t="n">
-        <v>0.004199213581852069</v>
+        <v>0.003477579320632029</v>
       </c>
       <c r="W39" t="n">
-        <v>0.004036201977016299</v>
+        <v>0.00389078326458341</v>
       </c>
       <c r="X39" t="n">
-        <v>0.003023760583938646</v>
+        <v>0.002971047251071547</v>
       </c>
     </row>
     <row r="40">
@@ -3611,61 +3611,61 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.3692825186777028</v>
+        <v>0.3243370001581284</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4129889766961385</v>
+        <v>0.3989329360059263</v>
       </c>
       <c r="M40" t="n">
-        <v>4.29006395973414</v>
+        <v>4.313508293409634</v>
       </c>
       <c r="N40" t="n">
-        <v>4.52315755862793</v>
+        <v>4.515674941600192</v>
       </c>
       <c r="O40" t="n">
-        <v>0.004352586472899283</v>
+        <v>0.004883390273872181</v>
       </c>
       <c r="P40" t="n">
-        <v>0.002746809176548628</v>
+        <v>0.002398670665872162</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.008913410651765246</v>
+        <v>0.005130170635277219</v>
       </c>
       <c r="R40" t="n">
-        <v>0.002597211481079451</v>
+        <v>0.002464980502542854</v>
       </c>
       <c r="S40" t="n">
-        <v>0.06881578154262762</v>
+        <v>0.05767348683769376</v>
       </c>
       <c r="T40" t="n">
-        <v>0.008767484861934733</v>
+        <v>0.01060725535288514</v>
       </c>
       <c r="U40" t="n">
-        <v>0.004053427229583141</v>
+        <v>0.003613989582990358</v>
       </c>
       <c r="V40" t="n">
-        <v>0.02952974972926173</v>
+        <v>0.01411408095501137</v>
       </c>
       <c r="W40" t="n">
-        <v>0.004137745408921228</v>
+        <v>0.004056990466028359</v>
       </c>
       <c r="X40" t="n">
-        <v>0.3234388347205902</v>
+        <v>0.2677956504505278</v>
       </c>
     </row>
     <row r="41">
@@ -3691,61 +3691,61 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2578830227728073</v>
+        <v>0.1959685484207236</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2872888890005925</v>
+        <v>0.2459190249821566</v>
       </c>
       <c r="M41" t="n">
-        <v>4.435303441664242</v>
+        <v>4.442693945177335</v>
       </c>
       <c r="N41" t="n">
-        <v>4.505865428394191</v>
+        <v>4.503036504899518</v>
       </c>
       <c r="O41" t="n">
-        <v>0.001885874797043332</v>
+        <v>0.00231770818268501</v>
       </c>
       <c r="P41" t="n">
-        <v>0.003090224114228162</v>
+        <v>0.002599171964452752</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.002032211494538419</v>
+        <v>0.001514242972042087</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0009525820710917798</v>
+        <v>0.0008795087260063928</v>
       </c>
       <c r="S41" t="n">
-        <v>0.003947123272506891</v>
+        <v>0.003634727561086875</v>
       </c>
       <c r="T41" t="n">
-        <v>0.004721537733589135</v>
+        <v>0.006353217242332766</v>
       </c>
       <c r="U41" t="n">
-        <v>0.005243173617153481</v>
+        <v>0.004715218560661922</v>
       </c>
       <c r="V41" t="n">
-        <v>0.005952751202613626</v>
+        <v>0.004150076829969573</v>
       </c>
       <c r="W41" t="n">
-        <v>0.002143613574384814</v>
+        <v>0.002073062958050786</v>
       </c>
       <c r="X41" t="n">
-        <v>0.006966141081336729</v>
+        <v>0.006551936789514502</v>
       </c>
     </row>
     <row r="42">
@@ -3771,61 +3771,61 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3188781726443401</v>
+        <v>0.2600786066317703</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4379210195285828</v>
+        <v>0.4003587216062984</v>
       </c>
       <c r="M42" t="n">
-        <v>4.54271279036458</v>
+        <v>4.567760363662879</v>
       </c>
       <c r="N42" t="n">
-        <v>4.559131111504287</v>
+        <v>4.547867196820644</v>
       </c>
       <c r="O42" t="n">
-        <v>0.004709091730122118</v>
+        <v>0.00527631899661574</v>
       </c>
       <c r="P42" t="n">
-        <v>0.003879590427411384</v>
+        <v>0.003016222279783191</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.01785842770497145</v>
+        <v>0.01093797541686029</v>
       </c>
       <c r="R42" t="n">
-        <v>0.00303571259298015</v>
+        <v>0.002862089165833362</v>
       </c>
       <c r="S42" t="n">
-        <v>1.000000000000011e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="T42" t="n">
-        <v>0.01258019030235064</v>
+        <v>0.02068617040798496</v>
       </c>
       <c r="U42" t="n">
-        <v>0.00892175609712932</v>
+        <v>0.01019984743437506</v>
       </c>
       <c r="V42" t="n">
-        <v>0.08712638832541059</v>
+        <v>0.05270328473226887</v>
       </c>
       <c r="W42" t="n">
-        <v>0.006574260282250777</v>
+        <v>0.006318111748244664</v>
       </c>
       <c r="X42" t="n">
-        <v>0.5345989055631742</v>
+        <v>0.9511565775523998</v>
       </c>
     </row>
     <row r="43">
@@ -3851,61 +3851,61 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2438232441219792</v>
+        <v>0.1847770070587039</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3810851628783983</v>
+        <v>0.320409186013875</v>
       </c>
       <c r="M43" t="n">
-        <v>4.004824234178307</v>
+        <v>3.931281342421583</v>
       </c>
       <c r="N43" t="n">
-        <v>4.259110168770842</v>
+        <v>4.237591806042442</v>
       </c>
       <c r="O43" t="n">
-        <v>0.02304987011556212</v>
+        <v>0.04442964346546929</v>
       </c>
       <c r="P43" t="n">
-        <v>0.01371149721923592</v>
+        <v>0.0138757994541428</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.05825984033178059</v>
+        <v>0.02645230570639786</v>
       </c>
       <c r="R43" t="n">
-        <v>0.02425003774073567</v>
+        <v>0.0180416577435934</v>
       </c>
       <c r="S43" t="n">
-        <v>0.06561790139053701</v>
+        <v>0.05846948392315802</v>
       </c>
       <c r="T43" t="n">
-        <v>0.05329263422510308</v>
+        <v>0.135760946159779</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02110716649765067</v>
+        <v>0.02230956611524275</v>
       </c>
       <c r="V43" t="n">
-        <v>0.2275533820289328</v>
+        <v>0.08102749913907925</v>
       </c>
       <c r="W43" t="n">
-        <v>0.04224216348717645</v>
+        <v>0.04111310776093187</v>
       </c>
       <c r="X43" t="n">
-        <v>0.1792849424645402</v>
+        <v>0.158900862248379</v>
       </c>
     </row>
     <row r="44">
@@ -3931,61 +3931,61 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1750004298657557</v>
+        <v>0.1168265495049782</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3277841145113169</v>
+        <v>0.2997327023322942</v>
       </c>
       <c r="M44" t="n">
-        <v>4.26677501303533</v>
+        <v>4.250053691127665</v>
       </c>
       <c r="N44" t="n">
-        <v>4.388906099140782</v>
+        <v>4.369655603421465</v>
       </c>
       <c r="O44" t="n">
-        <v>0.05523841796833086</v>
+        <v>0.08685026361533522</v>
       </c>
       <c r="P44" t="n">
-        <v>0.02242912332517252</v>
+        <v>0.02682898621294981</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.04130001213799385</v>
+        <v>0.02705206182328824</v>
       </c>
       <c r="R44" t="n">
-        <v>0.01124542818330652</v>
+        <v>0.01017648877893654</v>
       </c>
       <c r="S44" t="n">
-        <v>0.02245171420635166</v>
+        <v>0.01900367150708703</v>
       </c>
       <c r="T44" t="n">
-        <v>0.1662677252229182</v>
+        <v>0.3107426153187798</v>
       </c>
       <c r="U44" t="n">
-        <v>0.04069814013028705</v>
+        <v>0.06515612897456106</v>
       </c>
       <c r="V44" t="n">
-        <v>0.1496235450402074</v>
+        <v>0.07949079146785069</v>
       </c>
       <c r="W44" t="n">
-        <v>0.02142311010372736</v>
+        <v>0.02043865642472508</v>
       </c>
       <c r="X44" t="n">
-        <v>0.04611776250969853</v>
+        <v>0.039270011428226</v>
       </c>
     </row>
     <row r="45">
@@ -4011,61 +4011,61 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3970700662958236</v>
+        <v>0.3530798955686953</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3269920361240056</v>
+        <v>0.4388472945079925</v>
       </c>
       <c r="M45" t="n">
-        <v>4.224020019874794</v>
+        <v>4.170472779500921</v>
       </c>
       <c r="N45" t="n">
-        <v>4.376588707455891</v>
+        <v>4.433088135609349</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1183172323013069</v>
+        <v>0.1807364622369918</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1290516876741385</v>
+        <v>0.1528338742228456</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.151567191082598</v>
+        <v>0.07482038086892241</v>
       </c>
       <c r="R45" t="n">
-        <v>0.09413662262835801</v>
+        <v>0.08777549654071587</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1138836702494154</v>
+        <v>0.1085122831761504</v>
       </c>
       <c r="T45" t="n">
-        <v>0.5422051448390474</v>
+        <v>1.153023632505882</v>
       </c>
       <c r="U45" t="n">
-        <v>0.4101037140660773</v>
+        <v>0.6138067585891148</v>
       </c>
       <c r="V45" t="n">
-        <v>1.106649450776112</v>
+        <v>0.3250142105320909</v>
       </c>
       <c r="W45" t="n">
-        <v>0.2716016590243724</v>
+        <v>0.2461268743862165</v>
       </c>
       <c r="X45" t="n">
-        <v>0.4490887177443214</v>
+        <v>0.4015819041937621</v>
       </c>
     </row>
     <row r="46">
@@ -4091,61 +4091,61 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4191548341898909</v>
+        <v>0.4067201208266214</v>
       </c>
       <c r="L46" t="n">
-        <v>0.4168528808457668</v>
+        <v>0.465094401034203</v>
       </c>
       <c r="M46" t="n">
-        <v>3.769550246054656</v>
+        <v>3.808282305100428</v>
       </c>
       <c r="N46" t="n">
-        <v>4.479216138634888</v>
+        <v>4.469208613927203</v>
       </c>
       <c r="O46" t="n">
-        <v>0.06815244606365466</v>
+        <v>0.08059038517937758</v>
       </c>
       <c r="P46" t="n">
-        <v>0.04363101644153401</v>
+        <v>0.04943361346132352</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.1115269200480784</v>
+        <v>0.04460463973866373</v>
       </c>
       <c r="R46" t="n">
-        <v>0.03506941055577647</v>
+        <v>0.03545861834688241</v>
       </c>
       <c r="S46" t="n">
-        <v>0.1766596998023533</v>
+        <v>0.1655978876784426</v>
       </c>
       <c r="T46" t="n">
-        <v>0.1839301078095844</v>
+        <v>0.2358430308776615</v>
       </c>
       <c r="U46" t="n">
-        <v>0.08708392857054373</v>
+        <v>0.10470355008253</v>
       </c>
       <c r="V46" t="n">
-        <v>0.4252814507212731</v>
+        <v>0.1164883164149852</v>
       </c>
       <c r="W46" t="n">
-        <v>0.05383642207826184</v>
+        <v>0.05657768721927307</v>
       </c>
       <c r="X46" t="n">
-        <v>1.852554806219026</v>
+        <v>1.589133733935244</v>
       </c>
     </row>
     <row r="47">
@@ -4171,61 +4171,61 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.2534470292225203</v>
+        <v>0.1898361565792907</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3811388062430823</v>
+        <v>0.3170324206859707</v>
       </c>
       <c r="M47" t="n">
-        <v>4.285238971656212</v>
+        <v>4.207363086855939</v>
       </c>
       <c r="N47" t="n">
-        <v>4.355084664189493</v>
+        <v>4.332319379528892</v>
       </c>
       <c r="O47" t="n">
-        <v>0.03719789115727632</v>
+        <v>0.06418753791702034</v>
       </c>
       <c r="P47" t="n">
-        <v>0.0192020824216369</v>
+        <v>0.02508102916053349</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.06126978512097164</v>
+        <v>0.02591344311583163</v>
       </c>
       <c r="R47" t="n">
-        <v>0.01798217060741234</v>
+        <v>0.01427090144933693</v>
       </c>
       <c r="S47" t="n">
-        <v>0.02701672834624705</v>
+        <v>0.02075426605287888</v>
       </c>
       <c r="T47" t="n">
-        <v>0.0922260101293388</v>
+        <v>0.1957143218236412</v>
       </c>
       <c r="U47" t="n">
-        <v>0.03184278833795193</v>
+        <v>0.05752413428380904</v>
       </c>
       <c r="V47" t="n">
-        <v>0.2514649973089039</v>
+        <v>0.07869034439131588</v>
       </c>
       <c r="W47" t="n">
-        <v>0.03095129787733047</v>
+        <v>0.026470205203441</v>
       </c>
       <c r="X47" t="n">
-        <v>0.04978584852880755</v>
+        <v>0.03976262882243074</v>
       </c>
     </row>
     <row r="48">
@@ -4251,61 +4251,61 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1132798991704734</v>
+        <v>0.07057579079882771</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3961852980358451</v>
+        <v>0.4745752762180548</v>
       </c>
       <c r="M48" t="n">
-        <v>3.703826593445649</v>
+        <v>3.801459647451884</v>
       </c>
       <c r="N48" t="n">
-        <v>4.328103045292792</v>
+        <v>4.347047091259896</v>
       </c>
       <c r="O48" t="n">
-        <v>0.03608141213484152</v>
+        <v>0.03929900350856486</v>
       </c>
       <c r="P48" t="n">
-        <v>0.05217034402924473</v>
+        <v>0.05417157240514107</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.1190733979486861</v>
+        <v>0.1241591739825809</v>
       </c>
       <c r="R48" t="n">
-        <v>0.03932959554243818</v>
+        <v>0.04530971811799489</v>
       </c>
       <c r="S48" t="n">
-        <v>0.2373343859913021</v>
+        <v>0.2256831012710456</v>
       </c>
       <c r="T48" t="n">
-        <v>0.105073370176132</v>
+        <v>0.1231249764716775</v>
       </c>
       <c r="U48" t="n">
-        <v>0.115918779459669</v>
+        <v>0.1222769913184401</v>
       </c>
       <c r="V48" t="n">
-        <v>0.5973731506809006</v>
+        <v>0.5210320119382282</v>
       </c>
       <c r="W48" t="n">
-        <v>0.08880654171337501</v>
+        <v>0.08483266795404527</v>
       </c>
       <c r="X48" t="n">
-        <v>5.873755705300761</v>
+        <v>4.519125382949449</v>
       </c>
     </row>
     <row r="49">
@@ -4331,61 +4331,61 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3643052533076485</v>
+        <v>0.3223441909441093</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4626134843324982</v>
+        <v>0.4530260037366964</v>
       </c>
       <c r="M49" t="n">
-        <v>4.05609595904365</v>
+        <v>4.043607044971687</v>
       </c>
       <c r="N49" t="n">
-        <v>4.395311496622861</v>
+        <v>4.383995846359112</v>
       </c>
       <c r="O49" t="n">
-        <v>0.01913113267811397</v>
+        <v>0.02183775125969165</v>
       </c>
       <c r="P49" t="n">
-        <v>0.01227654661279837</v>
+        <v>0.01220224553277607</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.1012473966115392</v>
+        <v>0.04905244273263658</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01774762523272208</v>
+        <v>0.01733682755285186</v>
       </c>
       <c r="S49" t="n">
-        <v>0.09365734320220197</v>
+        <v>0.08667373452157981</v>
       </c>
       <c r="T49" t="n">
-        <v>0.03735966291437876</v>
+        <v>0.04638903603515153</v>
       </c>
       <c r="U49" t="n">
-        <v>0.01636004393131301</v>
+        <v>0.01621107564724511</v>
       </c>
       <c r="V49" t="n">
-        <v>0.407183587415602</v>
+        <v>0.1646129563276379</v>
       </c>
       <c r="W49" t="n">
-        <v>0.02713355284417511</v>
+        <v>0.02761662630678731</v>
       </c>
       <c r="X49" t="n">
-        <v>0.3255838314347613</v>
+        <v>0.291923069261095</v>
       </c>
     </row>
     <row r="50">
@@ -4411,61 +4411,61 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5041804397675377</v>
+        <v>0.4969413621409701</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5283724817625948</v>
+        <v>0.5558011348926327</v>
       </c>
       <c r="M50" t="n">
-        <v>4.245466267633814</v>
+        <v>4.269727495470134</v>
       </c>
       <c r="N50" t="n">
-        <v>4.524558493791908</v>
+        <v>4.552559913109352</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0870643850815126</v>
+        <v>0.07522103933914269</v>
       </c>
       <c r="P50" t="n">
-        <v>0.06649343178727672</v>
+        <v>0.0637517630761114</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.4950957030827258</v>
+        <v>0.2161791793253504</v>
       </c>
       <c r="R50" t="n">
-        <v>0.03299544411367916</v>
+        <v>0.03211954590151369</v>
       </c>
       <c r="S50" t="n">
-        <v>0.004429056687361941</v>
+        <v>0.00349161940464249</v>
       </c>
       <c r="T50" t="n">
-        <v>0.0002369187574658769</v>
+        <v>0.2223535233103695</v>
       </c>
       <c r="U50" t="n">
-        <v>0.1340819236589611</v>
+        <v>0.1196406222358911</v>
       </c>
       <c r="V50" t="n">
-        <v>2.297132503872639</v>
+        <v>0.8772386404210584</v>
       </c>
       <c r="W50" t="n">
-        <v>0.06795212325910853</v>
+        <v>0.05071067091516898</v>
       </c>
       <c r="X50" t="n">
-        <v>0.2650505668175427</v>
+        <v>0.6121742521796609</v>
       </c>
     </row>
     <row r="51">
@@ -4491,61 +4491,61 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.47819434822235</v>
+        <v>0.4799319100595422</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4658025015475036</v>
+        <v>0.5535747883704961</v>
       </c>
       <c r="M51" t="n">
-        <v>3.863171910508307</v>
+        <v>3.888757795315895</v>
       </c>
       <c r="N51" t="n">
-        <v>4.504246649878797</v>
+        <v>4.442650024333787</v>
       </c>
       <c r="O51" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.07935799048627404</v>
       </c>
       <c r="P51" t="n">
-        <v>0.09181491111050021</v>
+        <v>0.04976419921806362</v>
       </c>
       <c r="Q51" t="n">
         <v>0.4999999999999999</v>
       </c>
       <c r="R51" t="n">
-        <v>0.109564180638207</v>
+        <v>0.07574123568963934</v>
       </c>
       <c r="S51" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.2295652459480341</v>
       </c>
       <c r="T51" t="n">
-        <v>36.84678696159292</v>
+        <v>0.2280422724283145</v>
       </c>
       <c r="U51" t="n">
-        <v>0.2960437797136573</v>
+        <v>0.1018793922183666</v>
       </c>
       <c r="V51" t="n">
-        <v>5.672312533963903</v>
+        <v>2.075309702285547</v>
       </c>
       <c r="W51" t="n">
-        <v>0.4334352215314723</v>
+        <v>0.1435815110654676</v>
       </c>
       <c r="X51" t="n">
-        <v>28.85279960716459</v>
+        <v>2.706024554128635</v>
       </c>
     </row>
     <row r="52">
@@ -4571,61 +4571,61 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1606943136811414</v>
+        <v>0.1030582047638746</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3258488121138525</v>
+        <v>0.245699661210445</v>
       </c>
       <c r="M52" t="n">
-        <v>4.367592709598685</v>
+        <v>4.3471512475704</v>
       </c>
       <c r="N52" t="n">
-        <v>4.304345849735195</v>
+        <v>4.27932093195647</v>
       </c>
       <c r="O52" t="n">
-        <v>0.01559011913636744</v>
+        <v>0.0229852753930611</v>
       </c>
       <c r="P52" t="n">
-        <v>0.008592507796055511</v>
+        <v>0.009271876120134291</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.02659308178128166</v>
+        <v>0.01502695579423551</v>
       </c>
       <c r="R52" t="n">
-        <v>0.005967432658001913</v>
+        <v>0.004501576941872644</v>
       </c>
       <c r="S52" t="n">
-        <v>0.01993959391141046</v>
+        <v>0.01479814432843962</v>
       </c>
       <c r="T52" t="n">
-        <v>0.03672823729495082</v>
+        <v>0.06729399446284115</v>
       </c>
       <c r="U52" t="n">
-        <v>0.0166197342823487</v>
+        <v>0.02228388908260022</v>
       </c>
       <c r="V52" t="n">
-        <v>0.0858232788430276</v>
+        <v>0.04123251203429341</v>
       </c>
       <c r="W52" t="n">
-        <v>0.01435306706455114</v>
+        <v>0.01298268692998369</v>
       </c>
       <c r="X52" t="n">
-        <v>0.04672440451977132</v>
+        <v>0.04302576643890685</v>
       </c>
     </row>
     <row r="53">
@@ -4651,61 +4651,61 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3301843999480364</v>
+        <v>0.2718345787311342</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2240901512487175</v>
+        <v>0.2630965545361177</v>
       </c>
       <c r="M53" t="n">
-        <v>4.38210137775019</v>
+        <v>4.337572452346413</v>
       </c>
       <c r="N53" t="n">
-        <v>4.426651157655445</v>
+        <v>4.431692220656839</v>
       </c>
       <c r="O53" t="n">
-        <v>0.03852063928316336</v>
+        <v>0.05656158564803275</v>
       </c>
       <c r="P53" t="n">
-        <v>0.02203292985472621</v>
+        <v>0.02557519882363565</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.01662066593722407</v>
+        <v>0.01213188865711044</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02157825212368393</v>
+        <v>0.02115337376842716</v>
       </c>
       <c r="S53" t="n">
-        <v>0.06492062944712745</v>
+        <v>0.05978724444164666</v>
       </c>
       <c r="T53" t="n">
-        <v>0.08361079889747045</v>
+        <v>0.1460636694518522</v>
       </c>
       <c r="U53" t="n">
-        <v>0.03750899195664795</v>
+        <v>0.05095372448969718</v>
       </c>
       <c r="V53" t="n">
-        <v>0.04232456896730836</v>
+        <v>0.02595519905024486</v>
       </c>
       <c r="W53" t="n">
-        <v>0.03674217385693565</v>
+        <v>0.03783415389952461</v>
       </c>
       <c r="X53" t="n">
-        <v>0.0833636015477511</v>
+        <v>0.07653218184976915</v>
       </c>
     </row>
     <row r="54">
@@ -4731,61 +4731,61 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2281402508795552</v>
+        <v>0.1679007494998932</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4197763018584423</v>
+        <v>0.3993165688213579</v>
       </c>
       <c r="M54" t="n">
-        <v>4.229450565690408</v>
+        <v>4.211201045403707</v>
       </c>
       <c r="N54" t="n">
-        <v>4.316327871409245</v>
+        <v>4.295207199548182</v>
       </c>
       <c r="O54" t="n">
-        <v>0.02982374087718918</v>
+        <v>0.03670910439414624</v>
       </c>
       <c r="P54" t="n">
-        <v>0.009457457407215526</v>
+        <v>0.009667944098138504</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.07274148362977265</v>
+        <v>0.044479186747643</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009638236357850148</v>
+        <v>0.00869787689252938</v>
       </c>
       <c r="S54" t="n">
-        <v>0.02458778531551072</v>
+        <v>0.02230189355695891</v>
       </c>
       <c r="T54" t="n">
-        <v>0.07320749915717782</v>
+        <v>0.1034370869707226</v>
       </c>
       <c r="U54" t="n">
-        <v>0.01629820158756576</v>
+        <v>0.01649926373816254</v>
       </c>
       <c r="V54" t="n">
-        <v>0.2973900984894282</v>
+        <v>0.1525717368742169</v>
       </c>
       <c r="W54" t="n">
-        <v>0.01770352432181128</v>
+        <v>0.01810683908920906</v>
       </c>
       <c r="X54" t="n">
-        <v>0.04561879797058366</v>
+        <v>0.04242607336177236</v>
       </c>
     </row>
     <row r="55">
@@ -4811,61 +4811,61 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2002049545341849</v>
+        <v>0.1395613002756289</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4191732667833963</v>
+        <v>0.4425701077192274</v>
       </c>
       <c r="M55" t="n">
-        <v>4.431189175958969</v>
+        <v>4.453912052964032</v>
       </c>
       <c r="N55" t="n">
-        <v>4.390433459018819</v>
+        <v>4.387480692624546</v>
       </c>
       <c r="O55" t="n">
-        <v>0.02103738136053372</v>
+        <v>0.02316477675463279</v>
       </c>
       <c r="P55" t="n">
-        <v>0.009691691140620745</v>
+        <v>0.009822887072378335</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.06892321293224432</v>
+        <v>0.06554986118913313</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01324270397152735</v>
+        <v>0.01399349925932801</v>
       </c>
       <c r="S55" t="n">
-        <v>0.01246335935525229</v>
+        <v>0.01377379969731878</v>
       </c>
       <c r="T55" t="n">
-        <v>0.04716234335789923</v>
+        <v>0.05596868574085694</v>
       </c>
       <c r="U55" t="n">
-        <v>0.01606572015238173</v>
+        <v>0.01558748587581387</v>
       </c>
       <c r="V55" t="n">
-        <v>0.2267274849999288</v>
+        <v>0.195559668167211</v>
       </c>
       <c r="W55" t="n">
-        <v>0.0192464296814054</v>
+        <v>0.02064970110119516</v>
       </c>
       <c r="X55" t="n">
-        <v>0.0245563752012889</v>
+        <v>0.02567575765063713</v>
       </c>
     </row>
     <row r="56">
@@ -4891,61 +4891,61 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2084054602031741</v>
+        <v>0.1490350938530598</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3600930313309837</v>
+        <v>0.3130003395004233</v>
       </c>
       <c r="M56" t="n">
-        <v>4.062930613106723</v>
+        <v>4.00125006971951</v>
       </c>
       <c r="N56" t="n">
-        <v>4.325495710244655</v>
+        <v>4.300990731249425</v>
       </c>
       <c r="O56" t="n">
-        <v>0.02210648824806744</v>
+        <v>0.03136166837880883</v>
       </c>
       <c r="P56" t="n">
-        <v>0.01176598458901091</v>
+        <v>0.01355636486177632</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.04075638105339113</v>
+        <v>0.02257138592356472</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01410140152206501</v>
+        <v>0.0124107588552113</v>
       </c>
       <c r="S56" t="n">
-        <v>0.04455726009686568</v>
+        <v>0.04142768918841687</v>
       </c>
       <c r="T56" t="n">
-        <v>0.05061686586084162</v>
+        <v>0.08888577867181016</v>
       </c>
       <c r="U56" t="n">
-        <v>0.02061985347214569</v>
+        <v>0.02906462288831178</v>
       </c>
       <c r="V56" t="n">
-        <v>0.1520098973950142</v>
+        <v>0.06936069911019119</v>
       </c>
       <c r="W56" t="n">
-        <v>0.02442111072520134</v>
+        <v>0.02280688940987835</v>
       </c>
       <c r="X56" t="n">
-        <v>0.1119627520468515</v>
+        <v>0.105269825361745</v>
       </c>
     </row>
     <row r="57">
@@ -4971,61 +4971,61 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3825163888057561</v>
+        <v>0.3369187868683771</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4558533320374499</v>
+        <v>0.4319675110610038</v>
       </c>
       <c r="M57" t="n">
-        <v>4.276433697976676</v>
+        <v>4.255979924055767</v>
       </c>
       <c r="N57" t="n">
-        <v>4.373380090074489</v>
+        <v>4.360443573573453</v>
       </c>
       <c r="O57" t="n">
-        <v>0.02538363146635662</v>
+        <v>0.02937663718189853</v>
       </c>
       <c r="P57" t="n">
-        <v>0.00997545735538052</v>
+        <v>0.01073015857585876</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.08595078289326201</v>
+        <v>0.03711489628129596</v>
       </c>
       <c r="R57" t="n">
-        <v>0.01385699480007947</v>
+        <v>0.01290305073225852</v>
       </c>
       <c r="S57" t="n">
-        <v>0.02163546040652497</v>
+        <v>0.01943423316834082</v>
       </c>
       <c r="T57" t="n">
-        <v>0.05255138351840975</v>
+        <v>0.06500580921654261</v>
       </c>
       <c r="U57" t="n">
-        <v>0.01630445804602742</v>
+        <v>0.01887041573001512</v>
       </c>
       <c r="V57" t="n">
-        <v>0.3264916220278885</v>
+        <v>0.1153641534422299</v>
       </c>
       <c r="W57" t="n">
-        <v>0.02010057229666719</v>
+        <v>0.01963561255385254</v>
       </c>
       <c r="X57" t="n">
-        <v>0.03345048501093955</v>
+        <v>0.03083073092316636</v>
       </c>
     </row>
     <row r="58">
@@ -5051,61 +5051,61 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2320109535708661</v>
+        <v>0.1709595803976834</v>
       </c>
       <c r="L58" t="n">
-        <v>0.507533602320587</v>
+        <v>0.5062797879188051</v>
       </c>
       <c r="M58" t="n">
-        <v>4.248034418056246</v>
+        <v>4.217413991612381</v>
       </c>
       <c r="N58" t="n">
-        <v>4.459505725315455</v>
+        <v>4.444882040847515</v>
       </c>
       <c r="O58" t="n">
-        <v>0.06032972351979268</v>
+        <v>0.06868761647434823</v>
       </c>
       <c r="P58" t="n">
-        <v>0.01019892247551349</v>
+        <v>0.01007097611448617</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.2523265763185137</v>
+        <v>0.1380510321642458</v>
       </c>
       <c r="R58" t="n">
-        <v>0.009621218519374043</v>
+        <v>0.009022276078095904</v>
       </c>
       <c r="S58" t="n">
-        <v>0.05389884906893313</v>
+        <v>0.05053691460899772</v>
       </c>
       <c r="T58" t="n">
-        <v>0.1687872707202935</v>
+        <v>0.2104529181478092</v>
       </c>
       <c r="U58" t="n">
-        <v>0.01789661347076919</v>
+        <v>0.01780917771557993</v>
       </c>
       <c r="V58" t="n">
-        <v>1.920098256428989</v>
+        <v>0.7768348350921629</v>
       </c>
       <c r="W58" t="n">
-        <v>0.02015721931276533</v>
+        <v>0.01991390688654686</v>
       </c>
       <c r="X58" t="n">
-        <v>0.1154874332162085</v>
+        <v>0.1126229323644701</v>
       </c>
     </row>
     <row r="59">
@@ -5131,61 +5131,61 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4677808511850242</v>
+        <v>0.4429337950329169</v>
       </c>
       <c r="L59" t="n">
-        <v>0.515649168052881</v>
+        <v>0.5117118598911705</v>
       </c>
       <c r="M59" t="n">
-        <v>4.211580767596805</v>
+        <v>4.170892786605078</v>
       </c>
       <c r="N59" t="n">
-        <v>4.385713492739145</v>
+        <v>4.382706479156165</v>
       </c>
       <c r="O59" t="n">
-        <v>0.01105778307330017</v>
+        <v>0.012938841595171</v>
       </c>
       <c r="P59" t="n">
-        <v>0.004345440540321473</v>
+        <v>0.004588499984797221</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.1144390838443708</v>
+        <v>0.02889084174910219</v>
       </c>
       <c r="R59" t="n">
-        <v>0.006022792112750541</v>
+        <v>0.005694087223939987</v>
       </c>
       <c r="S59" t="n">
-        <v>0.007022642699285349</v>
+        <v>0.006522554144210779</v>
       </c>
       <c r="T59" t="n">
-        <v>0.01886039609919973</v>
+        <v>0.02353707247088712</v>
       </c>
       <c r="U59" t="n">
-        <v>0.005461442732465875</v>
+        <v>0.006009502286765845</v>
       </c>
       <c r="V59" t="n">
-        <v>0.4198095712585483</v>
+        <v>0.07877091497965838</v>
       </c>
       <c r="W59" t="n">
-        <v>0.005860135464004924</v>
+        <v>0.005677728764287528</v>
       </c>
       <c r="X59" t="n">
-        <v>0.006622152778646</v>
+        <v>0.006298999300228241</v>
       </c>
     </row>
     <row r="60">
@@ -5211,61 +5211,61 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3189569329734549</v>
+        <v>0.2695921991018025</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2352244177000707</v>
+        <v>0.2149184850172595</v>
       </c>
       <c r="M60" t="n">
-        <v>4.034948938354199</v>
+        <v>4.021231498279722</v>
       </c>
       <c r="N60" t="n">
-        <v>4.20670577107314</v>
+        <v>4.205633539409629</v>
       </c>
       <c r="O60" t="n">
-        <v>0.005140916073778912</v>
+        <v>0.008241467527600905</v>
       </c>
       <c r="P60" t="n">
-        <v>0.003592402431774052</v>
+        <v>0.003734552356181131</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.001837122072453943</v>
+        <v>0.001217605464887179</v>
       </c>
       <c r="R60" t="n">
-        <v>0.001655957385243227</v>
+        <v>0.00147210294664117</v>
       </c>
       <c r="S60" t="n">
-        <v>0.004692208695951013</v>
+        <v>0.004355688575257831</v>
       </c>
       <c r="T60" t="n">
-        <v>0.008957972913942772</v>
+        <v>0.01649763825184458</v>
       </c>
       <c r="U60" t="n">
-        <v>0.005505035720714246</v>
+        <v>0.006404388779868022</v>
       </c>
       <c r="V60" t="n">
-        <v>0.004777767969539658</v>
+        <v>0.002945604444029672</v>
       </c>
       <c r="W60" t="n">
-        <v>0.002288017436048617</v>
+        <v>0.00219284455410715</v>
       </c>
       <c r="X60" t="n">
-        <v>0.005390282671363266</v>
+        <v>0.005077915923142286</v>
       </c>
     </row>
     <row r="61">
@@ -5291,61 +5291,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4024729393044518</v>
+        <v>0.3818847677041697</v>
       </c>
       <c r="L61" t="n">
-        <v>0.3143833673945981</v>
+        <v>0.3619406545833125</v>
       </c>
       <c r="M61" t="n">
-        <v>3.85745491031177</v>
+        <v>3.900428030503485</v>
       </c>
       <c r="N61" t="n">
-        <v>4.247463635825699</v>
+        <v>4.264269376975633</v>
       </c>
       <c r="O61" t="n">
-        <v>0.007574281021108743</v>
+        <v>0.01022614180462163</v>
       </c>
       <c r="P61" t="n">
-        <v>0.007129931275491275</v>
+        <v>0.006645923183716829</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.007154865872353394</v>
+        <v>0.004015232455553099</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01053506682665868</v>
+        <v>0.01062583609331704</v>
       </c>
       <c r="S61" t="n">
-        <v>0.035892788464177</v>
+        <v>0.03259696007334879</v>
       </c>
       <c r="T61" t="n">
-        <v>0.01210282451562036</v>
+        <v>0.01993436644232748</v>
       </c>
       <c r="U61" t="n">
-        <v>0.008566000382406047</v>
+        <v>0.008097215788158871</v>
       </c>
       <c r="V61" t="n">
-        <v>0.01832407157048165</v>
+        <v>0.008181072222489989</v>
       </c>
       <c r="W61" t="n">
-        <v>0.009718497672040893</v>
+        <v>0.009816529112811468</v>
       </c>
       <c r="X61" t="n">
-        <v>0.1928318511527089</v>
+        <v>0.1514396387968307</v>
       </c>
     </row>
     <row r="62">
@@ -5371,61 +5371,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.42062216296563</v>
+        <v>0.3869191955124425</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2823433923516563</v>
+        <v>0.3437258291527271</v>
       </c>
       <c r="M62" t="n">
-        <v>4.186553856872338</v>
+        <v>4.172221392446892</v>
       </c>
       <c r="N62" t="n">
-        <v>4.213078996140245</v>
+        <v>4.236490806654437</v>
       </c>
       <c r="O62" t="n">
-        <v>0.01063162191662562</v>
+        <v>0.01313200703743985</v>
       </c>
       <c r="P62" t="n">
-        <v>0.004888036997275294</v>
+        <v>0.004914617694406478</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.007825323084788866</v>
+        <v>0.004943369388594487</v>
       </c>
       <c r="R62" t="n">
-        <v>0.01794699424673574</v>
+        <v>0.01814431607794239</v>
       </c>
       <c r="S62" t="n">
-        <v>0.01176308661090336</v>
+        <v>0.01176722655878575</v>
       </c>
       <c r="T62" t="n">
-        <v>0.02119125872045085</v>
+        <v>0.02957014926605848</v>
       </c>
       <c r="U62" t="n">
-        <v>0.009511091712022683</v>
+        <v>0.007931023198940913</v>
       </c>
       <c r="V62" t="n">
-        <v>0.02051298142471037</v>
+        <v>0.01018793448727281</v>
       </c>
       <c r="W62" t="n">
-        <v>0.02547641182911251</v>
+        <v>0.0269641422021395</v>
       </c>
       <c r="X62" t="n">
-        <v>0.02261406765143653</v>
+        <v>0.02258007601606412</v>
       </c>
     </row>
     <row r="63">
@@ -5451,61 +5451,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4155137200184437</v>
+        <v>0.3905045757093651</v>
       </c>
       <c r="L63" t="n">
-        <v>0.3139300893862646</v>
+        <v>0.3649604601070807</v>
       </c>
       <c r="M63" t="n">
-        <v>3.974111759233877</v>
+        <v>3.982649714136</v>
       </c>
       <c r="N63" t="n">
-        <v>4.245120077438735</v>
+        <v>4.256530599163072</v>
       </c>
       <c r="O63" t="n">
-        <v>0.00731338489943611</v>
+        <v>0.009167752545323199</v>
       </c>
       <c r="P63" t="n">
-        <v>0.006103920704866801</v>
+        <v>0.00556879038962906</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.006406327053050612</v>
+        <v>0.003893937915329071</v>
       </c>
       <c r="R63" t="n">
-        <v>0.008690094791090735</v>
+        <v>0.008821487837736366</v>
       </c>
       <c r="S63" t="n">
-        <v>0.01787753389454571</v>
+        <v>0.01721856491142366</v>
       </c>
       <c r="T63" t="n">
-        <v>0.01195832673304861</v>
+        <v>0.01748615502645201</v>
       </c>
       <c r="U63" t="n">
-        <v>0.007733867405802641</v>
+        <v>0.006685295715052205</v>
       </c>
       <c r="V63" t="n">
-        <v>0.0159928176958734</v>
+        <v>0.007694914962877258</v>
       </c>
       <c r="W63" t="n">
-        <v>0.009104066860956305</v>
+        <v>0.009540758297832273</v>
       </c>
       <c r="X63" t="n">
-        <v>0.0351760487450264</v>
+        <v>0.03306797223276946</v>
       </c>
     </row>
     <row r="64">
@@ -5531,61 +5531,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.375704959280303</v>
+        <v>0.353961587243898</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3426213014296025</v>
+        <v>0.3763285590018491</v>
       </c>
       <c r="M64" t="n">
-        <v>3.767070855148547</v>
+        <v>3.838905402431665</v>
       </c>
       <c r="N64" t="n">
-        <v>4.250864914093925</v>
+        <v>4.265074821365866</v>
       </c>
       <c r="O64" t="n">
-        <v>0.008313680814634754</v>
+        <v>0.0109197496530559</v>
       </c>
       <c r="P64" t="n">
-        <v>0.006626762266796679</v>
+        <v>0.006223120832633285</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.01218902888080777</v>
+        <v>0.006526225056539009</v>
       </c>
       <c r="R64" t="n">
-        <v>0.01893783953378358</v>
+        <v>0.01860606222009892</v>
       </c>
       <c r="S64" t="n">
-        <v>0.05208244477645838</v>
+        <v>0.04554320381016672</v>
       </c>
       <c r="T64" t="n">
-        <v>0.01566234637449351</v>
+        <v>0.02389715853995055</v>
       </c>
       <c r="U64" t="n">
-        <v>0.008395532442089087</v>
+        <v>0.007603508383933045</v>
       </c>
       <c r="V64" t="n">
-        <v>0.03364490491845272</v>
+        <v>0.01414820467761514</v>
       </c>
       <c r="W64" t="n">
-        <v>0.0276419386466147</v>
+        <v>0.02799118746100216</v>
       </c>
       <c r="X64" t="n">
-        <v>0.7520217731779802</v>
+        <v>0.5200282292025983</v>
       </c>
     </row>
     <row r="65">
@@ -5611,61 +5611,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4084703604096215</v>
+        <v>0.384443089336284</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3821916291466764</v>
+        <v>0.4105498185339166</v>
       </c>
       <c r="M65" t="n">
-        <v>3.911116290363315</v>
+        <v>3.924835681335463</v>
       </c>
       <c r="N65" t="n">
-        <v>4.272710125779127</v>
+        <v>4.279826125964913</v>
       </c>
       <c r="O65" t="n">
-        <v>0.008215030994181147</v>
+        <v>0.010302195519167</v>
       </c>
       <c r="P65" t="n">
-        <v>0.007855462868051768</v>
+        <v>0.007227611515985756</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.01694212333578252</v>
+        <v>0.008445430161853231</v>
       </c>
       <c r="R65" t="n">
-        <v>0.0112492040483913</v>
+        <v>0.01095139388704469</v>
       </c>
       <c r="S65" t="n">
-        <v>0.03281159232895717</v>
+        <v>0.03062183284305353</v>
       </c>
       <c r="T65" t="n">
-        <v>0.01322390061977321</v>
+        <v>0.0196879581203129</v>
       </c>
       <c r="U65" t="n">
-        <v>0.009802941309784341</v>
+        <v>0.008671932116099084</v>
       </c>
       <c r="V65" t="n">
-        <v>0.0470832531545477</v>
+        <v>0.01852554567665038</v>
       </c>
       <c r="W65" t="n">
-        <v>0.01165930398320151</v>
+        <v>0.01137781613420124</v>
       </c>
       <c r="X65" t="n">
-        <v>0.1282962353537908</v>
+        <v>0.1116734384006371</v>
       </c>
     </row>
     <row r="66">
@@ -5691,61 +5691,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3961978672711403</v>
+        <v>0.3670357668230109</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3293412087624536</v>
+        <v>0.3770322830656976</v>
       </c>
       <c r="M66" t="n">
-        <v>3.958594592841257</v>
+        <v>3.971214758552318</v>
       </c>
       <c r="N66" t="n">
-        <v>4.249439793462091</v>
+        <v>4.265461359393558</v>
       </c>
       <c r="O66" t="n">
-        <v>0.008695421175032979</v>
+        <v>0.01079622169470385</v>
       </c>
       <c r="P66" t="n">
-        <v>0.007122010709549243</v>
+        <v>0.006599611837300972</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.01106856049086037</v>
+        <v>0.006513284525454892</v>
       </c>
       <c r="R66" t="n">
-        <v>0.01648413762464574</v>
+        <v>0.01634544612879947</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0300757670190023</v>
+        <v>0.02868803240425893</v>
       </c>
       <c r="T66" t="n">
-        <v>0.01636464671352953</v>
+        <v>0.02336952957952134</v>
       </c>
       <c r="U66" t="n">
-        <v>0.00886178284415466</v>
+        <v>0.00787338372068676</v>
       </c>
       <c r="V66" t="n">
-        <v>0.02982990632975593</v>
+        <v>0.01404463834931119</v>
       </c>
       <c r="W66" t="n">
-        <v>0.02182603908776121</v>
+        <v>0.02243279383589959</v>
       </c>
       <c r="X66" t="n">
-        <v>0.1542475885411966</v>
+        <v>0.138110007790455</v>
       </c>
     </row>
     <row r="67">
@@ -5771,61 +5771,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.418401611669922</v>
+        <v>0.378033758727203</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3819472915502818</v>
+        <v>0.3947213665194616</v>
       </c>
       <c r="M67" t="n">
-        <v>4.381125636492835</v>
+        <v>4.37112257107835</v>
       </c>
       <c r="N67" t="n">
-        <v>4.3437415206267</v>
+        <v>4.339059934310458</v>
       </c>
       <c r="O67" t="n">
-        <v>0.005981321945530078</v>
+        <v>0.00771334183516295</v>
       </c>
       <c r="P67" t="n">
-        <v>0.01443185780472609</v>
+        <v>0.01400829248932625</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.01311134644951924</v>
+        <v>0.008832826891741431</v>
       </c>
       <c r="R67" t="n">
-        <v>0.009002841936241821</v>
+        <v>0.009646353555781839</v>
       </c>
       <c r="S67" t="n">
-        <v>0.04955294692193526</v>
+        <v>0.05276454314517653</v>
       </c>
       <c r="T67" t="n">
-        <v>0.009110887363966863</v>
+        <v>0.01218441112744616</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01313118042554026</v>
+        <v>0.0125362747752769</v>
       </c>
       <c r="V67" t="n">
-        <v>0.04752995067573015</v>
+        <v>0.02638129603029016</v>
       </c>
       <c r="W67" t="n">
-        <v>0.01285489229042732</v>
+        <v>0.01423506735731534</v>
       </c>
       <c r="X67" t="n">
-        <v>0.07785118174200721</v>
+        <v>0.07690151086321746</v>
       </c>
     </row>
     <row r="68">
@@ -5851,61 +5851,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4256809874704213</v>
+        <v>0.3818260119870678</v>
       </c>
       <c r="L68" t="n">
-        <v>0.37024086989327</v>
+        <v>0.3804433632154383</v>
       </c>
       <c r="M68" t="n">
-        <v>4.452681279498789</v>
+        <v>4.412285529802531</v>
       </c>
       <c r="N68" t="n">
-        <v>4.341149041498635</v>
+        <v>4.339395362258712</v>
       </c>
       <c r="O68" t="n">
-        <v>0.006850699174922427</v>
+        <v>0.009231917212703304</v>
       </c>
       <c r="P68" t="n">
-        <v>0.01736370747453858</v>
+        <v>0.01628437574162377</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.01389884232357233</v>
+        <v>0.007762453702357012</v>
       </c>
       <c r="R68" t="n">
-        <v>0.01344593217992822</v>
+        <v>0.01336135272836154</v>
       </c>
       <c r="S68" t="n">
-        <v>0.01471683289192487</v>
+        <v>0.01403469665102593</v>
       </c>
       <c r="T68" t="n">
-        <v>0.01276432462792603</v>
+        <v>0.01849211783055578</v>
       </c>
       <c r="U68" t="n">
-        <v>0.01608805234569639</v>
+        <v>0.01469460090193423</v>
       </c>
       <c r="V68" t="n">
-        <v>0.04205631454760868</v>
+        <v>0.01927769983464867</v>
       </c>
       <c r="W68" t="n">
-        <v>0.01918405262622363</v>
+        <v>0.02006569512838435</v>
       </c>
       <c r="X68" t="n">
-        <v>0.02478310122419881</v>
+        <v>0.0227738455583372</v>
       </c>
     </row>
     <row r="69">
@@ -5931,61 +5931,61 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1578375667668122</v>
+        <v>0.1011765085600368</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2144567936729055</v>
+        <v>0.1773044766578075</v>
       </c>
       <c r="M69" t="n">
-        <v>4.342039872316217</v>
+        <v>4.336669816495358</v>
       </c>
       <c r="N69" t="n">
-        <v>4.303184532172819</v>
+        <v>4.293565429207068</v>
       </c>
       <c r="O69" t="n">
-        <v>0.008246315744868482</v>
+        <v>0.01192085036804403</v>
       </c>
       <c r="P69" t="n">
-        <v>0.005349793618174257</v>
+        <v>0.005140067404071069</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.006110958250283045</v>
+        <v>0.004779986688728197</v>
       </c>
       <c r="R69" t="n">
-        <v>0.004326322131112634</v>
+        <v>0.003953450859161891</v>
       </c>
       <c r="S69" t="n">
-        <v>0.004195856823191065</v>
+        <v>0.003975182461431559</v>
       </c>
       <c r="T69" t="n">
-        <v>0.01779893935194048</v>
+        <v>0.03072204792244168</v>
       </c>
       <c r="U69" t="n">
-        <v>0.009261002924040385</v>
+        <v>0.01103774978648109</v>
       </c>
       <c r="V69" t="n">
-        <v>0.0138292357831867</v>
+        <v>0.009510092508828843</v>
       </c>
       <c r="W69" t="n">
-        <v>0.006098152479391987</v>
+        <v>0.005806384873026062</v>
       </c>
       <c r="X69" t="n">
-        <v>0.006144672343345428</v>
+        <v>0.005929783566498684</v>
       </c>
     </row>
     <row r="70">
@@ -6011,61 +6011,61 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1548404427189273</v>
+        <v>0.09853776886812335</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2803484396335723</v>
+        <v>0.2513895127329258</v>
       </c>
       <c r="M70" t="n">
-        <v>4.394470536415335</v>
+        <v>4.406147207166384</v>
       </c>
       <c r="N70" t="n">
-        <v>4.362026188385227</v>
+        <v>4.351024519902161</v>
       </c>
       <c r="O70" t="n">
-        <v>0.00683737974045138</v>
+        <v>0.008765521100579968</v>
       </c>
       <c r="P70" t="n">
-        <v>0.009679926537964173</v>
+        <v>0.01068221954004405</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.01029419268685945</v>
+        <v>0.007922641009322219</v>
       </c>
       <c r="R70" t="n">
-        <v>0.004619420786771253</v>
+        <v>0.004296356545144776</v>
       </c>
       <c r="S70" t="n">
-        <v>0.006474843743780381</v>
+        <v>0.006107706783452278</v>
       </c>
       <c r="T70" t="n">
-        <v>0.01330245434463462</v>
+        <v>0.02023648112270535</v>
       </c>
       <c r="U70" t="n">
-        <v>0.01366541402875141</v>
+        <v>0.01786036947290127</v>
       </c>
       <c r="V70" t="n">
-        <v>0.02670982624033935</v>
+        <v>0.0175526467522126</v>
       </c>
       <c r="W70" t="n">
-        <v>0.006677903647715045</v>
+        <v>0.006430910297688076</v>
       </c>
       <c r="X70" t="n">
-        <v>0.009672788733917848</v>
+        <v>0.009235210727375705</v>
       </c>
     </row>
     <row r="71">
@@ -6091,61 +6091,61 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3259506110927289</v>
+        <v>0.2686805224204179</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3487351942206435</v>
+        <v>0.3298379176249303</v>
       </c>
       <c r="M71" t="n">
-        <v>4.436154054572222</v>
+        <v>4.434548768386005</v>
       </c>
       <c r="N71" t="n">
-        <v>4.440319465156644</v>
+        <v>4.434143043383641</v>
       </c>
       <c r="O71" t="n">
-        <v>0.008528487484165495</v>
+        <v>0.01013475919470083</v>
       </c>
       <c r="P71" t="n">
-        <v>0.009241273042414807</v>
+        <v>0.008543614698053002</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.01207713702270264</v>
+        <v>0.007918245385571619</v>
       </c>
       <c r="R71" t="n">
-        <v>0.005169486642996195</v>
+        <v>0.004815296352703093</v>
       </c>
       <c r="S71" t="n">
-        <v>0.005569849868640615</v>
+        <v>0.005204764643569146</v>
       </c>
       <c r="T71" t="n">
-        <v>0.01410704170665147</v>
+        <v>0.01877846019129199</v>
       </c>
       <c r="U71" t="n">
-        <v>0.009886467507369101</v>
+        <v>0.009636368397903189</v>
       </c>
       <c r="V71" t="n">
-        <v>0.03237053463994669</v>
+        <v>0.01731433038885014</v>
       </c>
       <c r="W71" t="n">
-        <v>0.006798130412147313</v>
+        <v>0.006605738005774752</v>
       </c>
       <c r="X71" t="n">
-        <v>0.007000485893441635</v>
+        <v>0.00667178450941795</v>
       </c>
     </row>
     <row r="72">
@@ -6171,61 +6171,61 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3237573962818418</v>
+        <v>0.2657819781201773</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4164125635912082</v>
+        <v>0.3863103603617924</v>
       </c>
       <c r="M72" t="n">
-        <v>4.514536388254673</v>
+        <v>4.534002379268917</v>
       </c>
       <c r="N72" t="n">
-        <v>4.505611901814954</v>
+        <v>4.499145574022029</v>
       </c>
       <c r="O72" t="n">
-        <v>0.006054380605746239</v>
+        <v>0.006633208398129004</v>
       </c>
       <c r="P72" t="n">
-        <v>0.007017628670037607</v>
+        <v>0.006724645729910657</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.01932574713487418</v>
+        <v>0.01144681954947674</v>
       </c>
       <c r="R72" t="n">
-        <v>0.004440088622198801</v>
+        <v>0.004107308929607375</v>
       </c>
       <c r="S72" t="n">
-        <v>0.00611787710604061</v>
+        <v>0.005690126789497516</v>
       </c>
       <c r="T72" t="n">
-        <v>0.008824815817617734</v>
+        <v>0.01045793283686352</v>
       </c>
       <c r="U72" t="n">
-        <v>0.007879640720981459</v>
+        <v>0.007896627128392394</v>
       </c>
       <c r="V72" t="n">
-        <v>0.0562945012273876</v>
+        <v>0.02671937725093047</v>
       </c>
       <c r="W72" t="n">
-        <v>0.006203244904443203</v>
+        <v>0.005899612183437609</v>
       </c>
       <c r="X72" t="n">
-        <v>0.007784376618793378</v>
+        <v>0.007431302082436496</v>
       </c>
     </row>
     <row r="73">
@@ -6251,61 +6251,61 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.08006297265283152</v>
+        <v>0.04025470310716591</v>
       </c>
       <c r="L73" t="n">
-        <v>0.08137670514789817</v>
+        <v>0.05547139631089849</v>
       </c>
       <c r="M73" t="n">
-        <v>4.341883758983041</v>
+        <v>4.333373537311013</v>
       </c>
       <c r="N73" t="n">
-        <v>4.328688871169668</v>
+        <v>4.324632151484231</v>
       </c>
       <c r="O73" t="n">
-        <v>0.01318043929528642</v>
+        <v>0.02656051278654263</v>
       </c>
       <c r="P73" t="n">
-        <v>0.0125466430551157</v>
+        <v>0.01761088477961548</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.002167715958196518</v>
+        <v>0.001940807240261154</v>
       </c>
       <c r="R73" t="n">
-        <v>0.002549688039978831</v>
+        <v>0.002341227483811922</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003793148708945231</v>
+        <v>0.0002712346699651212</v>
       </c>
       <c r="T73" t="n">
-        <v>0.03799856800368664</v>
+        <v>0.09005882264789054</v>
       </c>
       <c r="U73" t="n">
-        <v>0.02527688761485034</v>
+        <v>0.04982984561406703</v>
       </c>
       <c r="V73" t="n">
-        <v>0.004536652955853525</v>
+        <v>0.00385627289056864</v>
       </c>
       <c r="W73" t="n">
-        <v>0.004164534776591435</v>
+        <v>0.004034216497276533</v>
       </c>
       <c r="X73" t="n">
-        <v>0.003228791926099474</v>
+        <v>0.003166052232820611</v>
       </c>
     </row>
     <row r="74">
@@ -6331,61 +6331,61 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08447647533141782</v>
+        <v>0.04323964746410821</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1660311016129161</v>
+        <v>0.1275131434332221</v>
       </c>
       <c r="M74" t="n">
-        <v>4.39908900615176</v>
+        <v>4.405756290037518</v>
       </c>
       <c r="N74" t="n">
-        <v>4.387721751732511</v>
+        <v>4.379623735245397</v>
       </c>
       <c r="O74" t="n">
-        <v>0.006072939442493623</v>
+        <v>0.009036393553288212</v>
       </c>
       <c r="P74" t="n">
-        <v>0.008410329726822863</v>
+        <v>0.009512190871382616</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.004647147445805709</v>
+        <v>0.003989002065271389</v>
       </c>
       <c r="R74" t="n">
-        <v>0.002118003523628594</v>
+        <v>0.001965770861115611</v>
       </c>
       <c r="S74" t="n">
-        <v>0.003735940490582123</v>
+        <v>0.003557275080640696</v>
       </c>
       <c r="T74" t="n">
-        <v>0.01595029981273453</v>
+        <v>0.02832272161273968</v>
       </c>
       <c r="U74" t="n">
-        <v>0.0142615260036707</v>
+        <v>0.02113690740729705</v>
       </c>
       <c r="V74" t="n">
-        <v>0.009537020261044847</v>
+        <v>0.007509248657619394</v>
       </c>
       <c r="W74" t="n">
-        <v>0.003689240799376155</v>
+        <v>0.003572465911428973</v>
       </c>
       <c r="X74" t="n">
-        <v>0.005621874364576946</v>
+        <v>0.005458596593377726</v>
       </c>
     </row>
     <row r="75">
@@ -6411,61 +6411,61 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.207879713293752</v>
+        <v>0.1486427815751791</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2637502655822012</v>
+        <v>0.2372415857304349</v>
       </c>
       <c r="M75" t="n">
-        <v>4.205773976883957</v>
+        <v>4.1963263632822</v>
       </c>
       <c r="N75" t="n">
-        <v>4.285330064989372</v>
+        <v>4.273131781469809</v>
       </c>
       <c r="O75" t="n">
-        <v>0.006159956762773762</v>
+        <v>0.008049330484596119</v>
       </c>
       <c r="P75" t="n">
-        <v>0.009588744945665553</v>
+        <v>0.01017478689827593</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.007587238447960803</v>
+        <v>0.005740851996500027</v>
       </c>
       <c r="R75" t="n">
-        <v>0.00478312747709922</v>
+        <v>0.004479090666957137</v>
       </c>
       <c r="S75" t="n">
-        <v>0.007195917205156532</v>
+        <v>0.006956014864066315</v>
       </c>
       <c r="T75" t="n">
-        <v>0.01213916372238912</v>
+        <v>0.01830197226282498</v>
       </c>
       <c r="U75" t="n">
-        <v>0.01262105451104735</v>
+        <v>0.01531091751475299</v>
       </c>
       <c r="V75" t="n">
-        <v>0.0181684843263972</v>
+        <v>0.0119442418441968</v>
       </c>
       <c r="W75" t="n">
-        <v>0.006550918900585312</v>
+        <v>0.006385456671668417</v>
       </c>
       <c r="X75" t="n">
-        <v>0.01090162797408519</v>
+        <v>0.0106358047943159</v>
       </c>
     </row>
     <row r="76">
@@ -6491,61 +6491,61 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02053128902279143</v>
+        <v>0.006369178025073023</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02508609221461723</v>
+        <v>0.01261258566047851</v>
       </c>
       <c r="M76" t="n">
-        <v>4.358945393733942</v>
+        <v>4.366980938685304</v>
       </c>
       <c r="N76" t="n">
-        <v>4.318049242587535</v>
+        <v>4.315739750622202</v>
       </c>
       <c r="O76" t="n">
-        <v>0.04219383556536199</v>
+        <v>0.1220354629072627</v>
       </c>
       <c r="P76" t="n">
-        <v>0.02731077098561718</v>
+        <v>0.06977388964247712</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.002159166246992141</v>
+        <v>0.002112399579899083</v>
       </c>
       <c r="R76" t="n">
-        <v>0.002217780159328968</v>
+        <v>0.002116109776265811</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0007945433877322265</v>
+        <v>0.0007606266878810434</v>
       </c>
       <c r="T76" t="n">
-        <v>0.1426419418644672</v>
+        <v>0.5012831288859023</v>
       </c>
       <c r="U76" t="n">
-        <v>0.08403595199388299</v>
+        <v>0.2848305626629655</v>
       </c>
       <c r="V76" t="n">
-        <v>0.003928934416035839</v>
+        <v>0.003653492107832782</v>
       </c>
       <c r="W76" t="n">
-        <v>0.003737555106552813</v>
+        <v>0.003680394987369161</v>
       </c>
       <c r="X76" t="n">
-        <v>0.002698768422105432</v>
+        <v>0.002684782231458661</v>
       </c>
     </row>
     <row r="77">
@@ -6571,61 +6571,61 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03789390692492493</v>
+        <v>0.01471419240858703</v>
       </c>
       <c r="L77" t="n">
-        <v>0.08292963581181916</v>
+        <v>0.04879795355628472</v>
       </c>
       <c r="M77" t="n">
-        <v>4.275909837651753</v>
+        <v>4.278059968673261</v>
       </c>
       <c r="N77" t="n">
-        <v>4.243110822914587</v>
+        <v>4.238087355601671</v>
       </c>
       <c r="O77" t="n">
-        <v>0.01335557096114733</v>
+        <v>0.02725600802704585</v>
       </c>
       <c r="P77" t="n">
-        <v>0.003709349423202523</v>
+        <v>0.003604208836173149</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.002379726884508766</v>
+        <v>0.002119454954673124</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0003763306604480696</v>
+        <v>0.0003389795294416913</v>
       </c>
       <c r="S77" t="n">
-        <v>0.001771409539367823</v>
+        <v>0.001687012383260638</v>
       </c>
       <c r="T77" t="n">
-        <v>0.03341861986133945</v>
+        <v>0.08448269531811869</v>
       </c>
       <c r="U77" t="n">
-        <v>0.01283848610580937</v>
+        <v>0.02077965702906235</v>
       </c>
       <c r="V77" t="n">
-        <v>0.004071085524943788</v>
+        <v>0.003436142524285324</v>
       </c>
       <c r="W77" t="n">
-        <v>0.002024296405620972</v>
+        <v>0.001995876991854825</v>
       </c>
       <c r="X77" t="n">
-        <v>0.002769094973651774</v>
+        <v>0.002714291076052019</v>
       </c>
     </row>
     <row r="78">
@@ -6651,61 +6651,61 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02722131315634268</v>
+        <v>0.009270839155371313</v>
       </c>
       <c r="L78" t="n">
-        <v>0.07757285863185416</v>
+        <v>0.04545609631557472</v>
       </c>
       <c r="M78" t="n">
-        <v>4.411801604657093</v>
+        <v>4.408817932135783</v>
       </c>
       <c r="N78" t="n">
-        <v>4.377579260969767</v>
+        <v>4.362545037288026</v>
       </c>
       <c r="O78" t="n">
-        <v>0.006191725781492362</v>
+        <v>0.01110894999695566</v>
       </c>
       <c r="P78" t="n">
-        <v>1.000000000015629e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.002055080234097392</v>
+        <v>0.00197147610529522</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0001676613644070592</v>
+        <v>0.0001285615819903837</v>
       </c>
       <c r="S78" t="n">
-        <v>1.000000000000053e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="T78" t="n">
-        <v>0.02127841748029065</v>
+        <v>0.04589527158411448</v>
       </c>
       <c r="U78" t="n">
-        <v>0.01842605984610099</v>
+        <v>0.0223009582419472</v>
       </c>
       <c r="V78" t="n">
-        <v>0.003649740698448271</v>
+        <v>0.003343603908246705</v>
       </c>
       <c r="W78" t="n">
-        <v>0.001708170741376304</v>
+        <v>0.00167453506465394</v>
       </c>
       <c r="X78" t="n">
-        <v>0.002929186528738509</v>
+        <v>0.003013550785088979</v>
       </c>
     </row>
     <row r="79">
@@ -6725,67 +6725,67 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.291298707758667</v>
+        <v>0.2303690117158935</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3305190424627622</v>
+        <v>0.2922880082219665</v>
       </c>
       <c r="M79" t="n">
-        <v>4.395075630781815</v>
+        <v>4.373390288550217</v>
       </c>
       <c r="N79" t="n">
-        <v>4.439000976856815</v>
+        <v>4.374687753223522</v>
       </c>
       <c r="O79" t="n">
-        <v>0.0030493650607155</v>
+        <v>0.003874377896894359</v>
       </c>
       <c r="P79" t="n">
-        <v>0.001822142396168952</v>
+        <v>0.0016599042526357</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.003531992673649635</v>
+        <v>0.002263333549891524</v>
       </c>
       <c r="R79" t="n">
-        <v>0.001661419250930073</v>
+        <v>0.001486610813278864</v>
       </c>
       <c r="S79" t="n">
-        <v>1.000000009297441e-05</v>
+        <v>0.4999999999999485</v>
       </c>
       <c r="T79" t="n">
-        <v>0.005999946057535997</v>
+        <v>0.009242686592394859</v>
       </c>
       <c r="U79" t="n">
-        <v>0.002118343938152528</v>
+        <v>0.002317044747122417</v>
       </c>
       <c r="V79" t="n">
-        <v>0.01106190708826921</v>
+        <v>0.005528595548609682</v>
       </c>
       <c r="W79" t="n">
-        <v>0.002607464827299831</v>
+        <v>0.002331140057399013</v>
       </c>
       <c r="X79" t="n">
-        <v>0.09212410143803679</v>
+        <v>11323.29021045563</v>
       </c>
     </row>
     <row r="80">
@@ -6805,67 +6805,67 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1623021847871931</v>
+        <v>0.1039261725912166</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2461521505440487</v>
+        <v>0.2177205905103834</v>
       </c>
       <c r="M80" t="n">
-        <v>4.51750010072576</v>
+        <v>4.528963221921295</v>
       </c>
       <c r="N80" t="n">
-        <v>4.473602328272493</v>
+        <v>4.423770408154914</v>
       </c>
       <c r="O80" t="n">
-        <v>0.004240554041854937</v>
+        <v>0.005951138760815349</v>
       </c>
       <c r="P80" t="n">
-        <v>0.002617430235380637</v>
+        <v>0.002696588537901111</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.003020996001069391</v>
+        <v>0.002332579388829773</v>
       </c>
       <c r="R80" t="n">
-        <v>0.001734728906689512</v>
+        <v>0.001592891305252286</v>
       </c>
       <c r="S80" t="n">
-        <v>1.000000000000011e-05</v>
+        <v>0.4999999999996049</v>
       </c>
       <c r="T80" t="n">
-        <v>0.01064745352376012</v>
+        <v>0.01822606393509635</v>
       </c>
       <c r="U80" t="n">
-        <v>0.003119576531330426</v>
+        <v>0.004384310329737579</v>
       </c>
       <c r="V80" t="n">
-        <v>0.008809571716300571</v>
+        <v>0.005608328160742104</v>
       </c>
       <c r="W80" t="n">
-        <v>0.002866173669782213</v>
+        <v>0.002570635045126057</v>
       </c>
       <c r="X80" t="n">
-        <v>0.1227993893269681</v>
+        <v>13524.07704700123</v>
       </c>
     </row>
     <row r="81">
@@ -6885,67 +6885,67 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.281196440943406</v>
+        <v>0.2166350389501655</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2613782739012544</v>
+        <v>0.2371417458613794</v>
       </c>
       <c r="M81" t="n">
-        <v>4.547853617806929</v>
+        <v>4.522784247933544</v>
       </c>
       <c r="N81" t="n">
-        <v>4.585463499527338</v>
+        <v>4.544896669458152</v>
       </c>
       <c r="O81" t="n">
-        <v>0.003803998975711694</v>
+        <v>0.005296059022033181</v>
       </c>
       <c r="P81" t="n">
-        <v>0.002242354063365949</v>
+        <v>0.00203526027187488</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.002110438349039313</v>
+        <v>0.001499616329197247</v>
       </c>
       <c r="R81" t="n">
-        <v>0.001625115970376529</v>
+        <v>0.001541782119411789</v>
       </c>
       <c r="S81" t="n">
-        <v>1.000000000000123e-05</v>
+        <v>0.4999999999728434</v>
       </c>
       <c r="T81" t="n">
-        <v>0.007875687776627336</v>
+        <v>0.01319379447680768</v>
       </c>
       <c r="U81" t="n">
-        <v>0.003196420059198681</v>
+        <v>0.003512461142381435</v>
       </c>
       <c r="V81" t="n">
-        <v>0.005902579127415904</v>
+        <v>0.003324158690234575</v>
       </c>
       <c r="W81" t="n">
-        <v>0.002513670493579258</v>
+        <v>0.002256930545991414</v>
       </c>
       <c r="X81" t="n">
-        <v>0.1086250010925224</v>
+        <v>17920.27500102449</v>
       </c>
     </row>
     <row r="82">
@@ -6965,67 +6965,67 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2355470167542912</v>
+        <v>0.1707707294026821</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1484167838956827</v>
+        <v>0.1532377929706163</v>
       </c>
       <c r="M82" t="n">
-        <v>4.463853060787375</v>
+        <v>4.419990824310435</v>
       </c>
       <c r="N82" t="n">
-        <v>4.586036636221306</v>
+        <v>4.604990570790342</v>
       </c>
       <c r="O82" t="n">
-        <v>0.006898595040632397</v>
+        <v>0.01125358544458983</v>
       </c>
       <c r="P82" t="n">
-        <v>0.003172162402697337</v>
+        <v>0.003082196799139005</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.001338179494625614</v>
+        <v>0.001120024918319054</v>
       </c>
       <c r="R82" t="n">
-        <v>0.001768550575490035</v>
+        <v>0.001753771990633061</v>
       </c>
       <c r="S82" t="n">
-        <v>0.09829178212853042</v>
+        <v>0.0009791743009648949</v>
       </c>
       <c r="T82" t="n">
-        <v>0.01808013244183422</v>
+        <v>0.03417867212766252</v>
       </c>
       <c r="U82" t="n">
-        <v>0.01244574955362399</v>
+        <v>0.009089674135542986</v>
       </c>
       <c r="V82" t="n">
-        <v>0.003310729654751748</v>
+        <v>0.00226060387953835</v>
       </c>
       <c r="W82" t="n">
-        <v>0.002634258504800033</v>
+        <v>0.002784361836071348</v>
       </c>
       <c r="X82" t="n">
-        <v>370.1227357116422</v>
+        <v>0.4459268266244293</v>
       </c>
     </row>
     <row r="83">
@@ -7045,65 +7045,65 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.189934792401037</v>
+        <v>0.1273374851235748</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1825649533455875</v>
+        <v>0.157400500745707</v>
       </c>
       <c r="M83" t="n">
-        <v>4.578578953049799</v>
+        <v>4.56844405665582</v>
       </c>
       <c r="N83" t="n">
-        <v>4.572070906719971</v>
+        <v>4.569187436921868</v>
       </c>
       <c r="O83" t="n">
-        <v>0.004176303540321362</v>
+        <v>0.006228560111931896</v>
       </c>
       <c r="P83" t="n">
-        <v>0.00171416512532195</v>
+        <v>0.001748406588302307</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.001440721495200495</v>
+        <v>0.001197211537960298</v>
       </c>
       <c r="R83" t="n">
-        <v>0.001422804646204883</v>
+        <v>0.001338320582679912</v>
       </c>
       <c r="S83" t="n">
-        <v>1.000000238964637e-05</v>
+        <v>1.000000000612286e-05</v>
       </c>
       <c r="T83" t="n">
-        <v>0.01015904721240343</v>
+        <v>0.01803997071749969</v>
       </c>
       <c r="U83" t="n">
-        <v>0.004949107285929085</v>
+        <v>0.006721020505277444</v>
       </c>
       <c r="V83" t="n">
-        <v>0.003728365474135352</v>
+        <v>0.002615807150191567</v>
       </c>
       <c r="W83" t="n">
-        <v>0.002372796481256224</v>
+        <v>0.00209822374099612</v>
       </c>
       <c r="X83" t="n">
-        <v>0.1285327874998751</v>
+        <v>0.1666386537309144</v>
       </c>
     </row>
     <row r="84">
@@ -7123,65 +7123,65 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.171344845273151</v>
+        <v>0.08008330526260318</v>
       </c>
       <c r="L84" t="n">
-        <v>0.3150855700217797</v>
+        <v>0.2347346333735086</v>
       </c>
       <c r="M84" t="n">
-        <v>4.585710978228106</v>
+        <v>3.382055805903954</v>
       </c>
       <c r="N84" t="n">
-        <v>4.514447225996494</v>
+        <v>4.453971427677734</v>
       </c>
       <c r="O84" t="n">
-        <v>0.00339100588623381</v>
+        <v>0.005104231222167039</v>
       </c>
       <c r="P84" t="n">
-        <v>0.0006915266427309581</v>
+        <v>1.000000000000145e-05</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.004446731886819412</v>
+        <v>0.002752311988366877</v>
       </c>
       <c r="R84" t="n">
-        <v>0.002270999306836499</v>
+        <v>0.001942772582694066</v>
       </c>
       <c r="S84" t="n">
-        <v>1e-05</v>
+        <v>0.4999999999999321</v>
       </c>
       <c r="T84" t="n">
-        <v>0.007793437798429175</v>
+        <v>0.01596272339679174</v>
       </c>
       <c r="U84" t="n">
-        <v>0.004561462884380771</v>
+        <v>0.005118553751037366</v>
       </c>
       <c r="V84" t="n">
-        <v>0.01460357726672547</v>
+        <v>0.007404730175260726</v>
       </c>
       <c r="W84" t="n">
-        <v>0.003725108105572998</v>
+        <v>0.003195418765320875</v>
       </c>
       <c r="X84" t="n">
-        <v>0.08015211397900641</v>
+        <v>13432.9369331339</v>
       </c>
     </row>
     <row r="85">
@@ -7201,65 +7201,67 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2347111018878213</v>
+        <v>0.232649974815383</v>
       </c>
       <c r="L85" t="n">
-        <v>0.295207682566716</v>
+        <v>0.2503677912979759</v>
       </c>
       <c r="M85" t="n">
-        <v>4.499856930037251</v>
+        <v>4.312526024436617</v>
       </c>
       <c r="N85" t="n">
-        <v>4.494031048189669</v>
+        <v>4.385938184561081</v>
       </c>
       <c r="O85" t="n">
-        <v>0.003123853781395702</v>
+        <v>0.004768096678336523</v>
       </c>
       <c r="P85" t="n">
-        <v>1.000000000701515e-05</v>
+        <v>0.001685538803218939</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.003071987961639764</v>
+        <v>0.001580410836808789</v>
       </c>
       <c r="R85" t="n">
-        <v>0.001784312597282091</v>
+        <v>0.001422356102245414</v>
       </c>
       <c r="S85" t="n">
-        <v>1.000000000000973e-05</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="T85" t="n">
-        <v>0.006948181082872566</v>
+        <v>0.01235886264802923</v>
       </c>
       <c r="U85" t="n">
-        <v>0.008318811544661376</v>
+        <v>0.003428135596984249</v>
       </c>
       <c r="V85" t="n">
-        <v>0.01012274793318518</v>
+        <v>0.003633335137743125</v>
       </c>
       <c r="W85" t="n">
-        <v>0.002901263572513301</v>
+        <v>0.002169788631533367</v>
       </c>
       <c r="X85" t="n">
-        <v>0.1105351683117262</v>
+        <v>18360.72015810333</v>
       </c>
     </row>
     <row r="86">
@@ -7279,65 +7281,67 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1247724149338163</v>
+        <v>0.1063207427095769</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1593628540125017</v>
+        <v>0.1881933317005607</v>
       </c>
       <c r="M86" t="n">
-        <v>4.570462719990509</v>
+        <v>4.515115790775487</v>
       </c>
       <c r="N86" t="n">
-        <v>4.515451460297303</v>
+        <v>4.436565061005309</v>
       </c>
       <c r="O86" t="n">
-        <v>0.005658362437520068</v>
+        <v>0.006787665072071847</v>
       </c>
       <c r="P86" t="n">
-        <v>1.000000000000045e-05</v>
+        <v>0.00272660493227992</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.001965539086526244</v>
+        <v>0.00192774752448879</v>
       </c>
       <c r="R86" t="n">
-        <v>0.001796124563344605</v>
+        <v>0.001602177685287185</v>
       </c>
       <c r="S86" t="n">
-        <v>1.000000002528958e-05</v>
+        <v>0.4999999999999994</v>
       </c>
       <c r="T86" t="n">
-        <v>0.01748892469336824</v>
+        <v>0.02145019925618195</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01076500190864138</v>
+        <v>0.006269128759394136</v>
       </c>
       <c r="V86" t="n">
-        <v>0.004959107179541152</v>
+        <v>0.004318345807380173</v>
       </c>
       <c r="W86" t="n">
-        <v>0.003011727484439199</v>
+        <v>0.00262564607667321</v>
       </c>
       <c r="X86" t="n">
-        <v>0.1599482502462652</v>
+        <v>21566.41144480819</v>
       </c>
     </row>
     <row r="87">
@@ -7357,65 +7361,67 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1836932525307708</v>
+        <v>0.1610958338338375</v>
       </c>
       <c r="L87" t="n">
-        <v>0.3217868630926628</v>
+        <v>0.1445709590857689</v>
       </c>
       <c r="M87" t="n">
-        <v>4.671001137082393</v>
+        <v>4.405149236767546</v>
       </c>
       <c r="N87" t="n">
-        <v>4.624548111189386</v>
+        <v>4.603720111448268</v>
       </c>
       <c r="O87" t="n">
-        <v>0.004065497993889858</v>
+        <v>0.01388825802591508</v>
       </c>
       <c r="P87" t="n">
-        <v>0.0005287890897613468</v>
+        <v>0.004175023338859141</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.004713074011125114</v>
+        <v>0.001238311138552735</v>
       </c>
       <c r="R87" t="n">
-        <v>0.002298817107172783</v>
+        <v>0.001944932478603518</v>
       </c>
       <c r="S87" t="n">
-        <v>1e-05</v>
+        <v>0.001028709409057571</v>
       </c>
       <c r="T87" t="n">
-        <v>0.009286549962721585</v>
+        <v>0.04536341368301234</v>
       </c>
       <c r="U87" t="n">
-        <v>0.006448785674556273</v>
+        <v>0.01168215052437232</v>
       </c>
       <c r="V87" t="n">
-        <v>0.01355658895827124</v>
+        <v>0.002401967695158536</v>
       </c>
       <c r="W87" t="n">
-        <v>0.00359377007022555</v>
+        <v>0.003143109781356395</v>
       </c>
       <c r="X87" t="n">
-        <v>0.08726200084236764</v>
+        <v>0.4655990751821463</v>
       </c>
     </row>
     <row r="88">
@@ -7435,65 +7441,67 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2269187336146035</v>
+        <v>0.2250426157877557</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1608077775199699</v>
+        <v>0.2454308346630373</v>
       </c>
       <c r="M88" t="n">
-        <v>4.508038569021577</v>
+        <v>4.524622090472267</v>
       </c>
       <c r="N88" t="n">
-        <v>4.616256352598314</v>
+        <v>4.546258464255389</v>
       </c>
       <c r="O88" t="n">
-        <v>0.005452932926096555</v>
+        <v>0.005592834545781133</v>
       </c>
       <c r="P88" t="n">
-        <v>0.000291810989428</v>
+        <v>0.002348660233268538</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.001197308778659838</v>
+        <v>0.001622315456437214</v>
       </c>
       <c r="R88" t="n">
-        <v>0.001397101994350155</v>
+        <v>0.001698413941012926</v>
       </c>
       <c r="S88" t="n">
-        <v>0.499999999571781</v>
+        <v>0.04148244992823262</v>
       </c>
       <c r="T88" t="n">
-        <v>0.01577093867425259</v>
+        <v>0.01416916565560014</v>
       </c>
       <c r="U88" t="n">
-        <v>0.01867328226824165</v>
+        <v>0.003636521560732845</v>
       </c>
       <c r="V88" t="n">
-        <v>0.003101299008548257</v>
+        <v>0.003587108757607886</v>
       </c>
       <c r="W88" t="n">
-        <v>0.002145340635275622</v>
+        <v>0.0024868416121757</v>
       </c>
       <c r="X88" t="n">
-        <v>20871.51586892164</v>
+        <v>122.5281590809826</v>
       </c>
     </row>
     <row r="89">
@@ -7513,65 +7521,65 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3488188784207902</v>
+        <v>0.288273972655646</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3410224706041754</v>
+        <v>0.2783510664376199</v>
       </c>
       <c r="M89" t="n">
-        <v>4.501604676162365</v>
+        <v>4.432624839498225</v>
       </c>
       <c r="N89" t="n">
-        <v>4.602245340539316</v>
+        <v>4.569726878751721</v>
       </c>
       <c r="O89" t="n">
-        <v>0.004115647714537776</v>
+        <v>0.005809602474994545</v>
       </c>
       <c r="P89" t="n">
-        <v>0.001578810907250336</v>
+        <v>0.0003769546208708393</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.00367226346658741</v>
+        <v>0.002011903240777739</v>
       </c>
       <c r="R89" t="n">
-        <v>0.001927730790878573</v>
+        <v>0.001770730009193956</v>
       </c>
       <c r="S89" t="n">
-        <v>1e-05</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="T89" t="n">
-        <v>0.008334293455075407</v>
+        <v>0.01526518233900631</v>
       </c>
       <c r="U89" t="n">
-        <v>0.004317875560936894</v>
+        <v>0.003395361843727251</v>
       </c>
       <c r="V89" t="n">
-        <v>0.01109477213261081</v>
+        <v>0.004688419138610027</v>
       </c>
       <c r="W89" t="n">
-        <v>0.002848415637878895</v>
+        <v>0.002586822410856835</v>
       </c>
       <c r="X89" t="n">
-        <v>0.06747476479493741</v>
+        <v>13182.32867399584</v>
       </c>
     </row>
     <row r="90">
@@ -7593,63 +7601,65 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5583518477656447</v>
+        <v>0.5704623921017763</v>
       </c>
       <c r="L90" t="n">
-        <v>0.5217627406001429</v>
+        <v>0.5274868623579249</v>
       </c>
       <c r="M90" t="n">
-        <v>4.519091781875822</v>
+        <v>4.52559509792863</v>
       </c>
       <c r="N90" t="n">
-        <v>4.274043771736172</v>
+        <v>4.292490031144113</v>
       </c>
       <c r="O90" t="n">
-        <v>0.004486479881857968</v>
+        <v>0.003941800627612678</v>
       </c>
       <c r="P90" t="n">
-        <v>0.003748094310035142</v>
+        <v>0.004488472383423079</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.2634453231136988</v>
+        <v>0.01297722075732921</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01263979615193675</v>
+        <v>0.01153259499344349</v>
       </c>
       <c r="S90" t="n">
-        <v>0.002949696252548581</v>
+        <v>0.003345395542123635</v>
       </c>
       <c r="T90" t="n">
-        <v>0.009701087912761794</v>
+        <v>0.00701816861107799</v>
       </c>
       <c r="U90" t="n">
-        <v>0.006098859879336028</v>
+        <v>0.005570567714143973</v>
       </c>
       <c r="V90" t="n">
-        <v>1.55051814407661</v>
+        <v>0.01961804486325159</v>
       </c>
       <c r="W90" t="n">
-        <v>0.03268548170545257</v>
+        <v>0.02789238866107401</v>
       </c>
       <c r="X90" t="n">
-        <v>0.08733761863442711</v>
+        <v>0.1121860405772075</v>
       </c>
     </row>
   </sheetData>
